--- a/신고신저가_20260721.xlsx
+++ b/신고신저가_20260721.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -74,13 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -449,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -607,7 +609,42 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 美 약보합·차익실현 vs 中 대형주 급반등(沪深300 +2.45%)이나 개별 신저 30개 — 지수·체감 괴리 확대 국면(추정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>■ 美: 3대지수 약보합(다우 -0.59%/나스닥 -0.05%/S&amp;P -0.19%). 금융(순강도+6)·에너지·유틸 강세, 전자기술·헬스테크 약세. AZN 임상실패 -2.6%·WBD 딜중단 -3.8%·QXO 인수희석 -6% 신저.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 日: 신고10/신저0, 보험·헬스테크 주도 자율반등. 소폼포 +4.2%(자사주 매입), 니폰스틸·다케다 신고가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>■ 中·홍콩: 상해 +1.22%·沪深300 +2.45%, 유틸(+4)·금융 견인 지수 강세이나 신저30(반도체·통신 조정)으로 양극화. 紫光股份 涨停(AI算力). 홍콩 HSI +0.10%·HSTECH +1.41%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①7/27~30 美 실적(AZN·LECO·캐논) ②中 지수강세 지속 vs 성장주 신저 확산 여부 ③유럽폭염 수혜 가전(Midea)·운임(SITC) 지속성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -708,7 +745,7 @@
       <c r="F2" t="n">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -743,7 +780,7 @@
       <c r="F3" t="n">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -778,7 +815,7 @@
       <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -813,7 +850,7 @@
       <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -848,7 +885,7 @@
       <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -883,7 +920,7 @@
       <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -918,7 +955,7 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -953,7 +990,7 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1163,7 +1200,7 @@
       <c r="F15" t="n">
         <v>-1</v>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1198,7 +1235,7 @@
       <c r="F16" t="n">
         <v>-1</v>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1233,7 +1270,7 @@
       <c r="F17" t="n">
         <v>-1</v>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1268,7 +1305,7 @@
       <c r="F18" t="n">
         <v>-1</v>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1303,7 +1340,7 @@
       <c r="F19" t="n">
         <v>-2</v>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1338,7 +1375,7 @@
       <c r="F20" t="n">
         <v>-2</v>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1373,7 +1410,7 @@
       <c r="F21" t="n">
         <v>-2</v>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1408,7 +1445,7 @@
       <c r="F22" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1443,7 +1480,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1478,7 +1515,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1513,7 +1550,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1548,7 +1585,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1583,7 +1620,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1618,7 +1655,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1653,7 +1690,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1688,7 +1725,7 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2038,7 +2075,7 @@
       <c r="F40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2073,7 +2110,7 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2598,7 +2635,7 @@
       <c r="F56" t="n">
         <v>-2</v>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2633,7 +2670,7 @@
       <c r="F57" t="n">
         <v>-2</v>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2668,7 +2705,7 @@
       <c r="F58" t="n">
         <v>4</v>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2703,7 +2740,7 @@
       <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2738,7 +2775,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2773,7 +2810,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3016,7 +3053,7 @@
       <c r="F68" t="n">
         <v>-1</v>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3049,7 +3086,7 @@
       <c r="F69" t="n">
         <v>-1</v>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3084,7 +3121,7 @@
       <c r="F70" t="n">
         <v>-1</v>
       </c>
-      <c r="G70" s="3" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3119,7 +3156,7 @@
       <c r="F71" t="n">
         <v>-2</v>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3154,7 +3191,7 @@
       <c r="F72" t="n">
         <v>-3</v>
       </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3189,7 +3226,7 @@
       <c r="F73" t="n">
         <v>-3</v>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3224,7 +3261,7 @@
       <c r="F74" t="n">
         <v>-6</v>
       </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3259,7 +3296,7 @@
       <c r="F75" t="n">
         <v>-10</v>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3439,55 +3476,55 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="6" t="n">
         <v>2.1</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="6" t="n">
         <v>6.7</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="6" t="n">
         <v>6.1</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="6" t="n">
         <v>31.4</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="6" t="n">
         <v>7.9</v>
       </c>
       <c r="K2" t="n">
         <v>8</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="6" t="n">
         <v>5.6</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="6" t="n">
         <v>-0.6</v>
       </c>
       <c r="O2" t="n">
         <v>9</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="P2" s="6" t="n">
         <v>64.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="R2" s="6" t="n">
         <v>53.3</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="T2" s="6" t="n">
         <v>-32.7</v>
       </c>
       <c r="U2" t="n">
@@ -3510,55 +3547,55 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="6" t="n">
         <v>-3.1</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="6" t="n">
         <v>-5.3</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="6" t="n">
         <v>22.3</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J3" s="6" t="n">
         <v>24.6</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="6" t="n">
         <v>21.6</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="6" t="n">
         <v>56</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="P3" s="6" t="n">
         <v>-27.7</v>
       </c>
       <c r="Q3" t="n">
         <v>9</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="R3" s="6" t="n">
         <v>34.7</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="T3" s="6" t="n">
         <v>43.6</v>
       </c>
       <c r="U3" t="n">
@@ -3581,55 +3618,55 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="6" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="6" t="n">
         <v>1.7</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="6" t="n">
         <v>-6.7</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="6" t="n">
         <v>-5.3</v>
       </c>
       <c r="I4" t="n">
         <v>11</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="6" t="n">
         <v>23.1</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="6" t="n">
         <v>34.7</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="6" t="n">
         <v>52.8</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="P4" s="6" t="n">
         <v>-37.6</v>
       </c>
       <c r="Q4" t="n">
         <v>11</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="R4" s="6" t="n">
         <v>16</v>
       </c>
       <c r="S4" t="n">
         <v>11</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="T4" s="6" t="n">
         <v>26.9</v>
       </c>
       <c r="U4" t="n">
@@ -3652,55 +3689,55 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="6" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="6" t="n">
         <v>3.8</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="6" t="n">
         <v>2.6</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="6" t="n">
         <v>13.8</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="6" t="n">
         <v>2.6</v>
       </c>
       <c r="K5" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="6" t="n">
         <v>5.1</v>
       </c>
       <c r="M5" t="n">
         <v>9</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="N5" s="6" t="n">
         <v>12.4</v>
       </c>
       <c r="O5" t="n">
         <v>6</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="P5" s="6" t="n">
         <v>-26.2</v>
       </c>
       <c r="Q5" t="n">
         <v>8</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="R5" s="6" t="n">
         <v>46.1</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="T5" s="6" t="n">
         <v>-2.2</v>
       </c>
       <c r="U5" t="n">
@@ -3723,55 +3760,55 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="6" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="6" t="n">
         <v>2.1</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="6" t="n">
         <v>3.6</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="6" t="n">
         <v>10.6</v>
       </c>
       <c r="I6" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
         <v>11</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="6" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" t="n">
         <v>7</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="6" t="n">
         <v>-0.8</v>
       </c>
       <c r="O6" t="n">
         <v>10</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="P6" s="6" t="n">
         <v>-0.8</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="R6" s="6" t="n">
         <v>17.2</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="T6" s="6" t="n">
         <v>10.1</v>
       </c>
       <c r="U6" t="n">
@@ -3794,55 +3831,55 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="6" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="6" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="6" t="n">
         <v>7.3</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="6" t="n">
         <v>3.2</v>
       </c>
       <c r="I7" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="6" t="n">
         <v>14.9</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="6" t="n">
         <v>30.6</v>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="6" t="n">
         <v>12</v>
       </c>
       <c r="O7" t="n">
         <v>7</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="P7" s="6" t="n">
         <v>-10.6</v>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="R7" s="6" t="n">
         <v>34.8</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="T7" s="6" t="n">
         <v>-1.7</v>
       </c>
       <c r="U7" t="n">
@@ -3865,55 +3902,55 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="6" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="6" t="n">
         <v>1.7</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="6" t="n">
         <v>-2</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="6" t="n">
         <v>6.7</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="6" t="n">
         <v>16</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="6" t="n">
         <v>23.3</v>
       </c>
       <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="6" t="n">
         <v>-7.2</v>
       </c>
       <c r="O8" t="n">
         <v>11</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="P8" s="6" t="n">
         <v>1.4</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="R8" s="6" t="n">
         <v>17.7</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="T8" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="U8" t="n">
@@ -3936,55 +3973,55 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="6" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="6" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="6" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="6" t="n">
         <v>2.9</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="6" t="n">
         <v>15.4</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="6" t="n">
         <v>19.3</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="6" t="n">
         <v>17.3</v>
       </c>
       <c r="M9" t="n">
         <v>6</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="N9" s="6" t="n">
         <v>18.1</v>
       </c>
       <c r="O9" t="n">
         <v>4</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="P9" s="6" t="n">
         <v>-5.6</v>
       </c>
       <c r="Q9" t="n">
         <v>5</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="R9" s="6" t="n">
         <v>21.1</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="T9" s="6" t="n">
         <v>10.9</v>
       </c>
       <c r="U9" t="n">
@@ -4007,55 +4044,55 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="6" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="6" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="6" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="6" t="n">
         <v>-4.6</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="6" t="n">
         <v>-3.6</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" s="6" t="n">
         <v>7.4</v>
       </c>
       <c r="K10" t="n">
         <v>9</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="6" t="n">
         <v>26.5</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="N10" s="6" t="n">
         <v>39.6</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="P10" s="6" t="n">
         <v>-36.3</v>
       </c>
       <c r="Q10" t="n">
         <v>10</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="R10" s="6" t="n">
         <v>27.9</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
       </c>
-      <c r="T10" s="4" t="n">
+      <c r="T10" s="6" t="n">
         <v>29.6</v>
       </c>
       <c r="U10" t="n">
@@ -4078,55 +4115,55 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="6" t="n">
         <v>-1</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="6" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="6" t="n">
         <v>-3.5</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="6" t="n">
         <v>-3.2</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="6" t="n">
         <v>11.2</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="6" t="n">
         <v>9.9</v>
       </c>
       <c r="K11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="6" t="n">
         <v>12.5</v>
       </c>
       <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="P11" s="6" t="n">
         <v>-12.3</v>
       </c>
       <c r="Q11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="R11" s="6" t="n">
         <v>27.4</v>
       </c>
       <c r="S11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="T11" s="6" t="n">
         <v>20.5</v>
       </c>
       <c r="U11" t="n">
@@ -4149,55 +4186,55 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="6" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="6" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="6" t="n">
         <v>6.1</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="6" t="n">
         <v>3.8</v>
       </c>
       <c r="I12" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" s="6" t="n">
         <v>14.5</v>
       </c>
       <c r="K12" t="n">
         <v>6</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="M12" t="n">
         <v>10</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="N12" s="6" t="n">
         <v>2.1</v>
       </c>
       <c r="O12" t="n">
         <v>8</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="P12" s="6" t="n">
         <v>-2.1</v>
       </c>
       <c r="Q12" t="n">
         <v>4</v>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="R12" s="6" t="n">
         <v>26</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="T12" s="6" t="n">
         <v>13.3</v>
       </c>
       <c r="U12" t="n">
@@ -4220,55 +4257,55 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="6" t="n">
         <v>-5.2</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="6" t="n">
         <v>-3.9</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="6" t="n">
         <v>19</v>
       </c>
       <c r="I13" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="6" t="n">
         <v>31.1</v>
       </c>
       <c r="K13" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="6" t="n">
         <v>22.3</v>
       </c>
       <c r="M13" t="n">
         <v>5</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="N13" s="6" t="n">
         <v>33.9</v>
       </c>
       <c r="O13" t="n">
         <v>6</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="P13" s="6" t="n">
         <v>-9.9</v>
       </c>
       <c r="Q13" t="n">
         <v>15</v>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="R13" s="6" t="n">
         <v>7.5</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
       </c>
-      <c r="T13" s="4" t="n">
+      <c r="T13" s="6" t="n">
         <v>17.7</v>
       </c>
       <c r="U13" t="n">
@@ -4291,55 +4328,55 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="6" t="n">
         <v>4.1</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="6" t="n">
         <v>2.9</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="6" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="6" t="n">
         <v>14.3</v>
       </c>
       <c r="I14" t="n">
         <v>8</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="6" t="n">
         <v>41.4</v>
       </c>
       <c r="K14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="6" t="n">
         <v>29.9</v>
       </c>
       <c r="M14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="N14" s="6" t="n">
         <v>37.2</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="P14" s="6" t="n">
         <v>23.6</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="R14" s="6" t="n">
         <v>39.3</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="T14" s="6" t="n">
         <v>-29</v>
       </c>
       <c r="U14" t="n">
@@ -4362,55 +4399,55 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="6" t="n">
         <v>3.9</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="6" t="n">
         <v>2.9</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="6" t="n">
         <v>6.3</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="6" t="n">
         <v>13.7</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="6" t="n">
         <v>28.9</v>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" s="6" t="n">
         <v>21.4</v>
       </c>
       <c r="K15" t="n">
         <v>10</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="6" t="n">
         <v>49</v>
       </c>
       <c r="M15" t="n">
         <v>2</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="N15" s="6" t="n">
         <v>27.2</v>
       </c>
       <c r="O15" t="n">
         <v>10</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="P15" s="6" t="n">
         <v>13.7</v>
       </c>
       <c r="Q15" t="n">
         <v>6</v>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="R15" s="6" t="n">
         <v>22.6</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
       </c>
-      <c r="T15" s="4" t="n">
+      <c r="T15" s="6" t="n">
         <v>-3.6</v>
       </c>
       <c r="U15" t="n">
@@ -4433,55 +4470,55 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="6" t="n">
         <v>3.1</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="6" t="n">
         <v>3.3</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="6" t="n">
         <v>2.1</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="6" t="n">
         <v>-8.9</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>15</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="J16" s="6" t="n">
         <v>37.4</v>
       </c>
       <c r="K16" t="n">
         <v>7</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" s="6" t="n">
         <v>6.3</v>
       </c>
       <c r="M16" t="n">
         <v>15</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="N16" s="6" t="n">
         <v>35</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="P16" s="6" t="n">
         <v>13.2</v>
       </c>
       <c r="Q16" t="n">
         <v>7</v>
       </c>
-      <c r="R16" s="4" t="n">
+      <c r="R16" s="6" t="n">
         <v>-8.300000000000001</v>
       </c>
       <c r="S16" t="n">
         <v>16</v>
       </c>
-      <c r="T16" s="4" t="n">
+      <c r="T16" s="6" t="n">
         <v>-10.7</v>
       </c>
       <c r="U16" t="n">
@@ -4504,55 +4541,55 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="6" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="6" t="n">
         <v>6.1</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="6" t="n">
         <v>18.8</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="6" t="n">
         <v>44.1</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="6" t="n">
         <v>44.8</v>
       </c>
       <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L17" s="6" t="n">
         <v>50.4</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="N17" s="6" t="n">
         <v>33.2</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
-      <c r="P17" s="4" t="n">
+      <c r="P17" s="6" t="n">
         <v>38.3</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R17" s="4" t="n">
+      <c r="R17" s="6" t="n">
         <v>26.7</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
       </c>
-      <c r="T17" s="4" t="n">
+      <c r="T17" s="6" t="n">
         <v>-16.3</v>
       </c>
       <c r="U17" t="n">
@@ -4575,55 +4612,55 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="6" t="n">
         <v>-3.7</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="6" t="n">
         <v>-22.5</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="6" t="n">
         <v>-17.2</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="6" t="n">
         <v>35.9</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="J18" s="6" t="n">
         <v>68.8</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="L18" s="6" t="n">
         <v>20.6</v>
       </c>
       <c r="M18" t="n">
         <v>8</v>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="6" t="n">
         <v>35</v>
       </c>
       <c r="O18" t="n">
         <v>4</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="P18" s="6" t="n">
         <v>16.1</v>
       </c>
       <c r="Q18" t="n">
         <v>5</v>
       </c>
-      <c r="R18" s="4" t="n">
+      <c r="R18" s="6" t="n">
         <v>20.8</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
       </c>
-      <c r="T18" s="4" t="n">
+      <c r="T18" s="6" t="n">
         <v>-8.6</v>
       </c>
       <c r="U18" t="n">
@@ -4646,55 +4683,55 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="6" t="n">
         <v>-7.7</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="6" t="n">
         <v>13.1</v>
       </c>
       <c r="I19" t="n">
         <v>9</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="6" t="n">
         <v>41.5</v>
       </c>
       <c r="K19" t="n">
         <v>5</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="6" t="n">
         <v>20.1</v>
       </c>
       <c r="M19" t="n">
         <v>9</v>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N19" s="6" t="n">
         <v>42</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="P19" s="6" t="n">
         <v>21.3</v>
       </c>
       <c r="Q19" t="n">
         <v>3</v>
       </c>
-      <c r="R19" s="4" t="n">
+      <c r="R19" s="6" t="n">
         <v>29.2</v>
       </c>
       <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T19" s="4" t="n">
+      <c r="T19" s="6" t="n">
         <v>1.9</v>
       </c>
       <c r="U19" t="n">
@@ -4717,55 +4754,55 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="6" t="n">
         <v>1.8</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="6" t="n">
         <v>-3.8</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="6" t="n">
         <v>-10.1</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="6" t="n">
         <v>12.5</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="6" t="n">
         <v>30.2</v>
       </c>
       <c r="I20" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="J20" s="6" t="n">
         <v>27.5</v>
       </c>
       <c r="K20" t="n">
         <v>9</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="6" t="n">
         <v>17.9</v>
       </c>
       <c r="M20" t="n">
         <v>10</v>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="6" t="n">
         <v>33.7</v>
       </c>
       <c r="O20" t="n">
         <v>7</v>
       </c>
-      <c r="P20" s="4" t="n">
+      <c r="P20" s="6" t="n">
         <v>-23</v>
       </c>
       <c r="Q20" t="n">
         <v>17</v>
       </c>
-      <c r="R20" s="4" t="n">
+      <c r="R20" s="6" t="n">
         <v>25</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
       </c>
-      <c r="T20" s="4" t="n">
+      <c r="T20" s="6" t="n">
         <v>26.2</v>
       </c>
       <c r="U20" t="n">
@@ -4788,55 +4825,55 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="6" t="n">
         <v>1.7</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="6" t="n">
         <v>6.2</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="6" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="I21" t="n">
         <v>16</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J21" s="6" t="n">
         <v>41.6</v>
       </c>
       <c r="K21" t="n">
         <v>4</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="6" t="n">
         <v>13.9</v>
       </c>
       <c r="M21" t="n">
         <v>12</v>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N21" s="6" t="n">
         <v>23.6</v>
       </c>
       <c r="O21" t="n">
         <v>11</v>
       </c>
-      <c r="P21" s="4" t="n">
+      <c r="P21" s="6" t="n">
         <v>4.4</v>
       </c>
       <c r="Q21" t="n">
         <v>11</v>
       </c>
-      <c r="R21" s="4" t="n">
+      <c r="R21" s="6" t="n">
         <v>6.8</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
-      <c r="T21" s="4" t="n">
+      <c r="T21" s="6" t="n">
         <v>-13.3</v>
       </c>
       <c r="U21" t="n">
@@ -4859,55 +4896,55 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="6" t="n">
         <v>4.2</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="6" t="n">
         <v>6.3</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="6" t="n">
         <v>-4.2</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="6" t="n">
         <v>-4.7</v>
       </c>
       <c r="I22" t="n">
         <v>17</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="J22" s="6" t="n">
         <v>13.5</v>
       </c>
       <c r="K22" t="n">
         <v>14</v>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="L22" s="6" t="n">
         <v>16.4</v>
       </c>
       <c r="M22" t="n">
         <v>11</v>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="N22" s="6" t="n">
         <v>40.5</v>
       </c>
       <c r="O22" t="n">
         <v>2</v>
       </c>
-      <c r="P22" s="4" t="n">
+      <c r="P22" s="6" t="n">
         <v>-10.7</v>
       </c>
       <c r="Q22" t="n">
         <v>16</v>
       </c>
-      <c r="R22" s="4" t="n">
+      <c r="R22" s="6" t="n">
         <v>27.8</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
       </c>
-      <c r="T22" s="4" t="n">
+      <c r="T22" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="U22" t="n">
@@ -4930,55 +4967,55 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="6" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="6" t="n">
         <v>3.1</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="6" t="n">
         <v>10.8</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="6" t="n">
         <v>5.7</v>
       </c>
       <c r="I23" t="n">
         <v>11</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" s="6" t="n">
         <v>13.9</v>
       </c>
       <c r="K23" t="n">
         <v>13</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="6" t="n">
         <v>21</v>
       </c>
       <c r="M23" t="n">
         <v>7</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="6" t="n">
         <v>17.9</v>
       </c>
       <c r="O23" t="n">
         <v>15</v>
       </c>
-      <c r="P23" s="4" t="n">
+      <c r="P23" s="6" t="n">
         <v>-5.9</v>
       </c>
       <c r="Q23" t="n">
         <v>13</v>
       </c>
-      <c r="R23" s="4" t="n">
+      <c r="R23" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="S23" t="n">
         <v>13</v>
       </c>
-      <c r="T23" s="4" t="n">
+      <c r="T23" s="6" t="n">
         <v>21.9</v>
       </c>
       <c r="U23" t="n">
@@ -5001,55 +5038,55 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="6" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="6" t="n">
         <v>-5.5</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="6" t="n">
         <v>10.4</v>
       </c>
       <c r="I24" t="n">
         <v>10</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="J24" s="6" t="n">
         <v>42</v>
       </c>
       <c r="K24" t="n">
         <v>3</v>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="L24" s="6" t="n">
         <v>21.6</v>
       </c>
       <c r="M24" t="n">
         <v>6</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="6" t="n">
         <v>32</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
-      <c r="P24" s="4" t="n">
+      <c r="P24" s="6" t="n">
         <v>-2.4</v>
       </c>
       <c r="Q24" t="n">
         <v>12</v>
       </c>
-      <c r="R24" s="4" t="n">
+      <c r="R24" s="6" t="n">
         <v>12.6</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
       </c>
-      <c r="T24" s="4" t="n">
+      <c r="T24" s="6" t="n">
         <v>-6.1</v>
       </c>
       <c r="U24" t="n">
@@ -5072,55 +5109,55 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="6" t="n">
         <v>2.6</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="6" t="n">
         <v>7.2</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="6" t="n">
         <v>-6.1</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="6" t="n">
         <v>2.9</v>
       </c>
       <c r="I25" t="n">
         <v>14</v>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" s="6" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>16</v>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="L25" s="6" t="n">
         <v>10.8</v>
       </c>
       <c r="M25" t="n">
         <v>13</v>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="N25" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="O25" t="n">
         <v>17</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="P25" s="6" t="n">
         <v>16.4</v>
       </c>
       <c r="Q25" t="n">
         <v>4</v>
       </c>
-      <c r="R25" s="4" t="n">
+      <c r="R25" s="6" t="n">
         <v>-8.4</v>
       </c>
       <c r="S25" t="n">
         <v>17</v>
       </c>
-      <c r="T25" s="4" t="n">
+      <c r="T25" s="6" t="n">
         <v>4.6</v>
       </c>
       <c r="U25" t="n">
@@ -5143,55 +5180,55 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="6" t="n">
         <v>3.2</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="6" t="n">
         <v>8.5</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="I26" t="n">
         <v>13</v>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="J26" s="6" t="n">
         <v>19.9</v>
       </c>
       <c r="K26" t="n">
         <v>11</v>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="L26" s="6" t="n">
         <v>-0</v>
       </c>
       <c r="M26" t="n">
         <v>17</v>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="N26" s="6" t="n">
         <v>19</v>
       </c>
       <c r="O26" t="n">
         <v>14</v>
       </c>
-      <c r="P26" s="4" t="n">
+      <c r="P26" s="6" t="n">
         <v>13.1</v>
       </c>
       <c r="Q26" t="n">
         <v>8</v>
       </c>
-      <c r="R26" s="4" t="n">
+      <c r="R26" s="6" t="n">
         <v>4.7</v>
       </c>
       <c r="S26" t="n">
         <v>12</v>
       </c>
-      <c r="T26" s="4" t="n">
+      <c r="T26" s="6" t="n">
         <v>-17.1</v>
       </c>
       <c r="U26" t="n">
@@ -5214,55 +5251,55 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="6" t="n">
         <v>4.1</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="6" t="n">
         <v>6.7</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="6" t="n">
         <v>16.6</v>
       </c>
       <c r="I27" t="n">
         <v>7</v>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J27" s="6" t="n">
         <v>11.8</v>
       </c>
       <c r="K27" t="n">
         <v>15</v>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="L27" s="6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>14</v>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N27" s="6" t="n">
         <v>22.3</v>
       </c>
       <c r="O27" t="n">
         <v>13</v>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="P27" s="6" t="n">
         <v>6.4</v>
       </c>
       <c r="Q27" t="n">
         <v>10</v>
       </c>
-      <c r="R27" s="4" t="n">
+      <c r="R27" s="6" t="n">
         <v>5.6</v>
       </c>
       <c r="S27" t="n">
         <v>11</v>
       </c>
-      <c r="T27" s="4" t="n">
+      <c r="T27" s="6" t="n">
         <v>-3.4</v>
       </c>
       <c r="U27" t="n">
@@ -5285,55 +5322,55 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="6" t="n">
         <v>6.6</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="6" t="n">
         <v>24.2</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="J28" s="6" t="n">
         <v>8.6</v>
       </c>
       <c r="K28" t="n">
         <v>17</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="6" t="n">
         <v>3.9</v>
       </c>
       <c r="M28" t="n">
         <v>16</v>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="6" t="n">
         <v>23.1</v>
       </c>
       <c r="O28" t="n">
         <v>12</v>
       </c>
-      <c r="P28" s="4" t="n">
+      <c r="P28" s="6" t="n">
         <v>-9.4</v>
       </c>
       <c r="Q28" t="n">
         <v>14</v>
       </c>
-      <c r="R28" s="4" t="n">
+      <c r="R28" s="6" t="n">
         <v>2.1</v>
       </c>
       <c r="S28" t="n">
         <v>14</v>
       </c>
-      <c r="T28" s="4" t="n">
+      <c r="T28" s="6" t="n">
         <v>8.6</v>
       </c>
       <c r="U28" t="n">
@@ -5356,55 +5393,55 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="6" t="n">
         <v>0.9</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="6" t="n">
         <v>4.7</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="6" t="n">
         <v>4.4</v>
       </c>
       <c r="I29" t="n">
         <v>12</v>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="J29" s="6" t="n">
         <v>16.8</v>
       </c>
       <c r="K29" t="n">
         <v>12</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="L29" s="6" t="n">
         <v>23.4</v>
       </c>
       <c r="M29" t="n">
         <v>4</v>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="N29" s="6" t="n">
         <v>16.4</v>
       </c>
       <c r="O29" t="n">
         <v>16</v>
       </c>
-      <c r="P29" s="4" t="n">
+      <c r="P29" s="6" t="n">
         <v>10.2</v>
       </c>
       <c r="Q29" t="n">
         <v>9</v>
       </c>
-      <c r="R29" s="4" t="n">
+      <c r="R29" s="6" t="n">
         <v>-4.4</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
       </c>
-      <c r="T29" s="4" t="n">
+      <c r="T29" s="6" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="U29" t="n">
@@ -5427,55 +5464,55 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="6" t="n">
         <v>2.3</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="6" t="n">
         <v>4.3</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="6" t="n">
         <v>-4.7</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="6" t="n">
         <v>-12.7</v>
       </c>
       <c r="I30" t="n">
         <v>3</v>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="J30" s="6" t="n">
         <v>22.7</v>
       </c>
       <c r="K30" t="n">
         <v>3</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="L30" s="6" t="n">
         <v>18.9</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="N30" s="6" t="n">
         <v>-9.300000000000001</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="P30" s="4" t="n">
+      <c r="P30" s="6" t="n">
         <v>-27.4</v>
       </c>
       <c r="Q30" t="n">
         <v>3</v>
       </c>
-      <c r="R30" s="4" t="n">
+      <c r="R30" s="6" t="n">
         <v>-32.9</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
       </c>
-      <c r="T30" s="4" t="inlineStr"/>
+      <c r="T30" s="6" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -5494,55 +5531,55 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="6" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="6" t="n">
         <v>2.9</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="6" t="n">
         <v>5.3</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="6" t="n">
         <v>-2.6</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="6" t="n">
         <v>-0.3</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="J31" s="6" t="n">
         <v>32.8</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="L31" s="6" t="n">
         <v>24.8</v>
       </c>
       <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="N31" s="4" t="n">
+      <c r="N31" s="6" t="n">
         <v>-11.9</v>
       </c>
       <c r="O31" t="n">
         <v>2</v>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="P31" s="6" t="n">
         <v>-14.4</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R31" s="4" t="n">
+      <c r="R31" s="6" t="n">
         <v>-13.5</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
-      <c r="T31" s="4" t="n">
+      <c r="T31" s="6" t="n">
         <v>-1.2</v>
       </c>
       <c r="U31" t="n">
@@ -5565,55 +5602,55 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="6" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="6" t="n">
         <v>2.9</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="6" t="n">
         <v>5.2</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="6" t="n">
         <v>-4.4</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="6" t="n">
         <v>-5.2</v>
       </c>
       <c r="I32" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="J32" s="6" t="n">
         <v>26.2</v>
       </c>
       <c r="K32" t="n">
         <v>2</v>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="L32" s="6" t="n">
         <v>32.1</v>
       </c>
       <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="N32" s="6" t="n">
         <v>-12.8</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="P32" s="6" t="n">
         <v>-17.8</v>
       </c>
       <c r="Q32" t="n">
         <v>2</v>
       </c>
-      <c r="R32" s="4" t="n">
+      <c r="R32" s="6" t="n">
         <v>-23.6</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
       </c>
-      <c r="T32" s="4" t="n">
+      <c r="T32" s="6" t="n">
         <v>-2</v>
       </c>
       <c r="U32" t="n">
@@ -5636,55 +5673,55 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="6" t="n">
         <v>-13.3</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="6" t="n">
         <v>-11.1</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="6" t="n">
         <v>39.3</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="6" t="n">
         <v>54.9</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J33" s="6" t="n">
         <v>45</v>
       </c>
       <c r="K33" t="n">
         <v>4</v>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="L33" s="6" t="n">
         <v>25.6</v>
       </c>
       <c r="M33" t="n">
         <v>2</v>
       </c>
-      <c r="N33" s="4" t="n">
+      <c r="N33" s="6" t="n">
         <v>-2.4</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="4" t="n">
+      <c r="P33" s="6" t="n">
         <v>-36.6</v>
       </c>
       <c r="Q33" t="n">
         <v>9</v>
       </c>
-      <c r="R33" s="4" t="n">
+      <c r="R33" s="6" t="n">
         <v>23.8</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
       </c>
-      <c r="T33" s="4" t="n">
+      <c r="T33" s="6" t="n">
         <v>46.2</v>
       </c>
       <c r="U33" t="n">
@@ -5707,55 +5744,55 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="6" t="n">
         <v>6.6</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="6" t="n">
         <v>-10.7</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="6" t="n">
         <v>-15</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="6" t="n">
         <v>20.4</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="6" t="n">
         <v>36.4</v>
       </c>
       <c r="I34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="J34" s="6" t="n">
         <v>52.1</v>
       </c>
       <c r="K34" t="n">
         <v>3</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="L34" s="6" t="n">
         <v>12</v>
       </c>
       <c r="M34" t="n">
         <v>4</v>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N34" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="O34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="4" t="n">
+      <c r="P34" s="6" t="n">
         <v>-34</v>
       </c>
       <c r="Q34" t="n">
         <v>8</v>
       </c>
-      <c r="R34" s="4" t="n">
+      <c r="R34" s="6" t="n">
         <v>-2.8</v>
       </c>
       <c r="S34" t="n">
         <v>6</v>
       </c>
-      <c r="T34" s="4" t="n">
+      <c r="T34" s="6" t="n">
         <v>44</v>
       </c>
       <c r="U34" t="n">
@@ -5778,55 +5815,55 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="6" t="n">
         <v>6.2</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="6" t="n">
         <v>-12.5</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="6" t="n">
         <v>-23.2</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="6" t="n">
         <v>12.4</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="6" t="n">
         <v>42.4</v>
       </c>
       <c r="I35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="J35" s="6" t="n">
         <v>99.7</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="L35" s="6" t="n">
         <v>24.2</v>
       </c>
       <c r="M35" t="n">
         <v>3</v>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="6" t="n">
         <v>16.3</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="4" t="n">
+      <c r="P35" s="6" t="n">
         <v>-37.8</v>
       </c>
       <c r="Q35" t="n">
         <v>10</v>
       </c>
-      <c r="R35" s="4" t="n">
+      <c r="R35" s="6" t="n">
         <v>6.8</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
       </c>
-      <c r="T35" s="4" t="n">
+      <c r="T35" s="6" t="n">
         <v>19.3</v>
       </c>
       <c r="U35" t="n">
@@ -5849,55 +5886,55 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="6" t="n">
         <v>-4.1</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="6" t="n">
         <v>-20.8</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="6" t="n">
         <v>-22.6</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="H36" s="6" t="n">
         <v>-16.4</v>
       </c>
       <c r="I36" t="n">
         <v>7</v>
       </c>
-      <c r="J36" s="4" t="n">
+      <c r="J36" s="6" t="n">
         <v>56.6</v>
       </c>
       <c r="K36" t="n">
         <v>2</v>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="L36" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="M36" t="n">
         <v>6</v>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="N36" s="6" t="n">
         <v>-29</v>
       </c>
       <c r="O36" t="n">
         <v>9</v>
       </c>
-      <c r="P36" s="4" t="n">
+      <c r="P36" s="6" t="n">
         <v>-28.9</v>
       </c>
       <c r="Q36" t="n">
         <v>7</v>
       </c>
-      <c r="R36" s="4" t="n">
+      <c r="R36" s="6" t="n">
         <v>41.9</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="4" t="inlineStr"/>
+      <c r="T36" s="6" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -5916,55 +5953,55 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="6" t="n">
         <v>2.3</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="6" t="n">
         <v>-6.8</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="6" t="n">
         <v>-16.9</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="6" t="n">
         <v>-22.2</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="6" t="n">
         <v>-21.4</v>
       </c>
       <c r="I37" t="n">
         <v>10</v>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J37" s="6" t="n">
         <v>31.8</v>
       </c>
       <c r="K37" t="n">
         <v>5</v>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="L37" s="6" t="n">
         <v>8.5</v>
       </c>
       <c r="M37" t="n">
         <v>5</v>
       </c>
-      <c r="N37" s="4" t="n">
+      <c r="N37" s="6" t="n">
         <v>-10.8</v>
       </c>
       <c r="O37" t="n">
         <v>5</v>
       </c>
-      <c r="P37" s="4" t="n">
+      <c r="P37" s="6" t="n">
         <v>-26.1</v>
       </c>
       <c r="Q37" t="n">
         <v>5</v>
       </c>
-      <c r="R37" s="4" t="n">
+      <c r="R37" s="6" t="n">
         <v>13.1</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
       </c>
-      <c r="T37" s="4" t="n">
+      <c r="T37" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="U37" t="n">
@@ -5987,55 +6024,55 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="6" t="n">
         <v>-6.1</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="6" t="n">
         <v>-23.1</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="6" t="n">
         <v>-25.1</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H38" s="6" t="n">
         <v>-16.6</v>
       </c>
       <c r="I38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="J38" s="6" t="n">
         <v>27.1</v>
       </c>
       <c r="K38" t="n">
         <v>6</v>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="L38" s="6" t="n">
         <v>-14.9</v>
       </c>
       <c r="M38" t="n">
         <v>10</v>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="N38" s="6" t="n">
         <v>-35.2</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
-      <c r="P38" s="4" t="n">
+      <c r="P38" s="6" t="n">
         <v>-19.7</v>
       </c>
       <c r="Q38" t="n">
         <v>3</v>
       </c>
-      <c r="R38" s="4" t="n">
+      <c r="R38" s="6" t="n">
         <v>50.7</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="4" t="inlineStr"/>
+      <c r="T38" s="6" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -6054,55 +6091,55 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="6" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="6" t="n">
         <v>0.9</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="6" t="n">
         <v>3.5</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="6" t="n">
         <v>-8</v>
       </c>
       <c r="I39" t="n">
         <v>5</v>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="J39" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="K39" t="n">
         <v>8</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="L39" s="6" t="n">
         <v>29.7</v>
       </c>
       <c r="M39" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="N39" s="6" t="n">
         <v>3.8</v>
       </c>
       <c r="O39" t="n">
         <v>2</v>
       </c>
-      <c r="P39" s="4" t="n">
+      <c r="P39" s="6" t="n">
         <v>-26.1</v>
       </c>
       <c r="Q39" t="n">
         <v>5</v>
       </c>
-      <c r="R39" s="4" t="n">
+      <c r="R39" s="6" t="n">
         <v>-3.8</v>
       </c>
       <c r="S39" t="n">
         <v>8</v>
       </c>
-      <c r="T39" s="4" t="n">
+      <c r="T39" s="6" t="n">
         <v>17.5</v>
       </c>
       <c r="U39" t="n">
@@ -6125,55 +6162,55 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="6" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="6" t="n">
         <v>-1.3</v>
       </c>
       <c r="I40" t="n">
         <v>4</v>
       </c>
-      <c r="J40" s="4" t="n">
+      <c r="J40" s="6" t="n">
         <v>4.7</v>
       </c>
       <c r="K40" t="n">
         <v>7</v>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="L40" s="6" t="n">
         <v>-12.2</v>
       </c>
       <c r="M40" t="n">
         <v>9</v>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="N40" s="6" t="n">
         <v>-14</v>
       </c>
       <c r="O40" t="n">
         <v>6</v>
       </c>
-      <c r="P40" s="4" t="n">
+      <c r="P40" s="6" t="n">
         <v>-24.5</v>
       </c>
       <c r="Q40" t="n">
         <v>4</v>
       </c>
-      <c r="R40" s="4" t="n">
+      <c r="R40" s="6" t="n">
         <v>-15.7</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
       </c>
-      <c r="T40" s="4" t="n">
+      <c r="T40" s="6" t="n">
         <v>58.4</v>
       </c>
       <c r="U40" t="n">
@@ -6196,55 +6233,55 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="6" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="6" t="n">
         <v>6.9</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="6" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="6" t="n">
         <v>-15.5</v>
       </c>
       <c r="I41" t="n">
         <v>6</v>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="J41" s="6" t="n">
         <v>-2.9</v>
       </c>
       <c r="K41" t="n">
         <v>9</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="L41" s="6" t="n">
         <v>-4.2</v>
       </c>
       <c r="M41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="4" t="n">
+      <c r="N41" s="6" t="n">
         <v>-18.3</v>
       </c>
       <c r="O41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="4" t="n">
+      <c r="P41" s="6" t="n">
         <v>-13.4</v>
       </c>
       <c r="Q41" t="n">
         <v>2</v>
       </c>
-      <c r="R41" s="4" t="n">
+      <c r="R41" s="6" t="n">
         <v>-7.5</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
       </c>
-      <c r="T41" s="4" t="n">
+      <c r="T41" s="6" t="n">
         <v>72.7</v>
       </c>
       <c r="U41" t="n">
@@ -6267,55 +6304,55 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="6" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="6" t="n">
         <v>7.3</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="6" t="n">
         <v>-12.4</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="6" t="n">
         <v>-20.7</v>
       </c>
       <c r="I42" t="n">
         <v>9</v>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="J42" s="6" t="n">
         <v>-13</v>
       </c>
       <c r="K42" t="n">
         <v>10</v>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="L42" s="6" t="n">
         <v>-11</v>
       </c>
       <c r="M42" t="n">
         <v>8</v>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="N42" s="6" t="n">
         <v>-18.6</v>
       </c>
       <c r="O42" t="n">
         <v>8</v>
       </c>
-      <c r="P42" s="4" t="n">
+      <c r="P42" s="6" t="n">
         <v>-11.9</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
-      <c r="R42" s="4" t="n">
+      <c r="R42" s="6" t="n">
         <v>-3</v>
       </c>
       <c r="S42" t="n">
         <v>7</v>
       </c>
-      <c r="T42" s="4" t="n">
+      <c r="T42" s="6" t="n">
         <v>302.8</v>
       </c>
       <c r="U42" t="n">
@@ -6338,23 +6375,23 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr"/>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
+      <c r="D43" s="6" t="inlineStr"/>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr"/>
+      <c r="J43" s="6" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" s="4" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="4" t="inlineStr"/>
+      <c r="N43" s="6" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" s="4" t="inlineStr"/>
+      <c r="P43" s="6" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" s="4" t="inlineStr"/>
+      <c r="R43" s="6" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
-      <c r="T43" s="4" t="inlineStr"/>
+      <c r="T43" s="6" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -6373,23 +6410,23 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr"/>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" s="4" t="inlineStr"/>
+      <c r="J44" s="6" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr"/>
+      <c r="N44" s="6" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" s="4" t="inlineStr"/>
+      <c r="P44" s="6" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" s="4" t="inlineStr"/>
+      <c r="R44" s="6" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
-      <c r="T44" s="4" t="inlineStr"/>
+      <c r="T44" s="6" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -6408,23 +6445,23 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr"/>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr"/>
+      <c r="D45" s="6" t="inlineStr"/>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" s="4" t="inlineStr"/>
+      <c r="J45" s="6" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="4" t="inlineStr"/>
+      <c r="N45" s="6" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" s="4" t="inlineStr"/>
+      <c r="P45" s="6" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" s="4" t="inlineStr"/>
+      <c r="R45" s="6" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
-      <c r="T45" s="4" t="inlineStr"/>
+      <c r="T45" s="6" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
     </row>
     <row r="47">
@@ -6663,12 +6700,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6711,15 +6748,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>TopBuild $170억 인수완료 30% 희석+주택착공허가 2.4% 감소로 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6760,15 +6801,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>UBS 분사 후 중립(목표 $231) 개시로 기대 미달, -4%대 급락</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6807,15 +6852,19 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>캘리포니아 판사, 파라마운트·스카이댄스 $1100억 딜 8/3까지 중단 명령</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6856,15 +6905,19 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>용접장비 수요 부진·고밸류 부담 지속, 7/30 실적 앞 관망 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6905,15 +6958,19 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>CARDIO-TTRansform Ph3 1차 평가변수 실패 여파, 7/27 실적 앞 불안</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6952,15 +7009,15 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7005,15 +7062,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7054,15 +7111,15 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7107,10 +7164,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7160,10 +7217,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7211,10 +7268,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7258,14 +7315,14 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>(전일) 2Q 실적 미스+호주 제련소 사고로 알루미나 가이던스 하향</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7311,10 +7368,10 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="6" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7364,14 +7421,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>(전일) 개별 촉매 없이 바이오 섹터 매도세 속 52주 신저가</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7419,19 +7476,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>(전일) HCA發 수술량 둔화 우려·목표가 인하($585→$520), 7/16 실적 앞 매도</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7476,15 +7533,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>바클레이즈 목표가 $21→$23 상향+트루이스트 매수 재확인, 원유 인프라 수급 호조</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7525,15 +7586,19 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="6" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>7/15 분기배당($0.176) 선언+재생에너지 확장 모멘텀, 7/30 실적 기대</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7574,15 +7639,19 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="6" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>창업자 맥킴 회장 퇴임·신임 의장 취임 거버넌스 전환 속 신고가 지속</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7627,15 +7696,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>S&amp;P400 편입(7/17)+UBS·BTIG·BofA 목표가 상향, 신고가 후 소폭 조정</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7676,15 +7749,19 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="6" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>시민증권 목표가 $100→$120 상향 불구 시장 전반 차익실현 매도</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7725,10 +7802,10 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="6" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7774,10 +7851,10 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="6" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7827,10 +7904,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7880,10 +7957,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7933,14 +8010,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="6" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>(전일) 정유·에너지 섹터 강세 동반(개별 뉴스 미확인)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7990,14 +8067,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>(전일) 정제마진 강세 지속, 애널리스트 목표가 상향 랠리</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8041,10 +8118,10 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="6" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8094,14 +8171,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>(전일) 정제 업황 호조, Raymond James TP $235 상향·정유 동반 강세</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8151,10 +8228,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M30" s="6" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8204,10 +8281,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8255,10 +8332,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8308,14 +8385,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M33" s="6" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>(전일) 2Q EPS $10.04(예상 $5.34) 대폭 서프라이즈, 재해손실 감소 +8%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8365,10 +8442,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M34" s="6" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8418,14 +8495,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr">
         <is>
           <t>(전일) General Mills·월마트 재생농업 제휴 발표+BMO 목표가 상향</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8475,10 +8552,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M36" s="6" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8528,10 +8605,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="6" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8581,10 +8658,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M38" s="6" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8634,10 +8711,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8687,7 +8764,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="6" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M40"/>
@@ -8787,12 +8864,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8837,15 +8914,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>보험섹터 상위·소폼포 690억엔 자사주매입 지속으로 수급 개선</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8886,15 +8967,19 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>US스틸 철강가 호조·FY27 이익 1000억엔 기여 기대로 자율반등</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8933,15 +9018,19 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>7/2 인실리코 AI 신약발굴 딜(~$600M) 재료+7/30 결산 앞둔 매수</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8982,15 +9071,19 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>광범위 자율반등+7/27 결산 앞둔 매수, 통기 순익 소폭 증가 예상</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9031,15 +9124,19 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>6/29 EU CHMP 다토포타마브 승인 권고+I-DXd FDA 우선심사 모멘텀</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9080,15 +9177,15 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9133,15 +9230,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9186,10 +9283,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9235,14 +9332,14 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>(전일) 디펜시브 소비재로 급락장서 상대적 견조, 60일 신고가</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9292,7 +9389,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>(전일) 기계·비철 급락장서 고배당 디펜시브로 상대 자금 유입</t>
         </is>
@@ -9396,7 +9493,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9442,14 +9539,14 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>(전일) 탄산리튬 가격 3월래 최저(칠레 수출증가·CATL 광산 재가동 공급과잉 우려)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9499,14 +9596,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>(전일) 골드만 하반기 리튬 20%+ 공급과잉 전망 등 공급증가 우려</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9552,14 +9649,14 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>(전일) 노무라 경쟁심화 경고·광섬유 가격 둔화 우려, 고점 차익실현</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9607,19 +9704,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>(전일) PCB·전자부품 섹터 급락(A주 동종 다수 하한가) 동반 하락</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9660,15 +9757,19 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>SCFI 4년래 신고가·중동 지정학 리스크로 아시아 역내 운임 반등 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9713,7 +9814,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>유럽 폭염으로 에어컨 수출 폭증(서유럽 +70%), 지속 자사주 매입 지지</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M7"/>
@@ -9813,12 +9918,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9857,15 +9962,19 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>2Q 순이익 환비 하락(-6~30%)+美 메모리주 급락 연동, 신저가 후 반등</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9906,15 +10015,19 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>리튬가격 지속 하락·기관 중간보고 확정 매도로 신저가 후 단기 반등</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9955,15 +10068,19 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>1Q 순이익 -47% YoY·5G사이클 조정·AI 수익화 지연, 신저가 후 반등</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10004,15 +10121,19 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>6월 80억 위안 정증 발행 계획 희석 우려로 신저가 후 기술적 반등</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10053,15 +10174,19 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>H1 순이익 +50~60% 예증·7/17 자사주 매입으로 하한가 후 낙폭 회복</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10102,15 +10227,15 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10151,15 +10276,15 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10198,15 +10323,15 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10247,15 +10372,15 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10296,15 +10421,15 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="6" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10345,15 +10470,15 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="6" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10394,15 +10519,15 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="6" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10443,15 +10568,15 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="6" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10492,15 +10617,15 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10541,15 +10666,15 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="6" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10590,15 +10715,15 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="6" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10639,10 +10764,10 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="6" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10690,10 +10815,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10741,14 +10866,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>(전일) IPO 직후 급락 지속: 패널 업황·370억위안 부채·해금 부담(7/3~7 이상변동)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10794,10 +10919,10 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="6" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10843,10 +10968,10 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="6" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10892,14 +11017,14 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="6" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>(전일) 1Q 순손실 확대(-77% YoY), 상업우주 테마 고점 차익실현</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10945,14 +11070,14 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="6" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>(전일) 1Q26 순이익 -62% 급감·주력자금 순유출, 고평가(PE 300배+) 부담 조정</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11000,14 +11125,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>(전일) 7/13 급락(-13%) 후 차익실현·주력자금 순유출 지속</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11053,14 +11178,14 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="6" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>(전일) 탄산리튬 가격 약세 지속·리튬 섹터 수급 부진</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11106,14 +11231,14 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="6" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>(전일) 1Q 순익 -30.7%·환차손 확대, 주력자금 순매도</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11159,10 +11284,10 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="6" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11208,10 +11333,10 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="6" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11257,14 +11382,14 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="6" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>(전일) 반기 가이던스(+25~45%)가 기관 예상(68%) 하회, PE 106배 해소</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11310,19 +11435,19 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>(전일) 반기 순익 +3200% 예고에도 대주주 감자 계획·고밸류 차익실현</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11367,15 +11492,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>AI算力·신화삼 매출급증+상반기 순이익 83~123% 증가 예고로 연속 涨停</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11416,15 +11545,19 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="6" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>이구환신 정책 수혜·글로벌 가전 판매 견조로 섹터 상승 동반 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11465,15 +11598,19 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="6" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>상반기 발전량 동비 +4.14%·홍수기 호조로 수력발전주 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11514,15 +11651,19 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="6" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>7/20 상반기 업적예증(컨테이너 처리량 +6.2% YoY) 반영 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11563,15 +11704,19 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="6" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>1Q 실적 안정·채널개혁 성과 기대감으로 섹터 수급 주도 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11616,15 +11761,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="6" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11669,15 +11814,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M38" s="6" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11718,15 +11863,15 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="6" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11767,15 +11912,15 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="6" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11814,10 +11959,10 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="6" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11863,7 +12008,7 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="6" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>(전일) 야룽장 유역 강수 증가로 수력 발전량 상승 기대</t>
         </is>

--- a/신고신저가_20260721.xlsx
+++ b/신고신저가_20260721.xlsx
@@ -611,7 +611,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>💬 ■ 결론: 美 약보합·차익실현 vs 中 대형주 급반등(沪深300 +2.45%)이나 개별 신저 30개 — 지수·체감 괴리 확대 국면(추정).</t>
+          <t>💬 ■ 결론: 美 약보합·차익실현 vs 中 대형주 급반등(CSI300 +2.45%)이나 개별 신저 30개 — 지수·체감 괴리 확대 국면(추정).</t>
         </is>
       </c>
     </row>
@@ -632,14 +632,14 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ 中·홍콩: 상해 +1.22%·沪深300 +2.45%, 유틸(+4)·금융 견인 지수 강세이나 신저30(반도체·통신 조정)으로 양극화. 紫光股份 涨停(AI算力). 홍콩 HSI +0.10%·HSTECH +1.41%.</t>
+          <t>■ 中·홍콩: 상해 +1.22%·CSI300 +2.45%, 유틸(+4)·금융 견인 지수 강세이나 신저30(반도체·통신 조정)으로 양극화. 쯔광구펀(H3C 서버·네트워크장비) 상한가. 홍콩 HSI +0.10%·HSTECH +1.41%.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ 체크: ①7/27~30 美 실적(AZN·LECO·캐논) ②中 지수강세 지속 vs 성장주 신저 확산 여부 ③유럽폭염 수혜 가전(Midea)·운임(SITC) 지속성.</t>
+          <t>■ 체크: ①7/27~30 美 실적(AZN·LECO·캐논) ②中 지수강세 지속 vs 성장주 신저 확산 여부 ③유럽폭염 수혜 가전(메이디)·해운운임(SITC) 지속성.</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>CARDIO-TTRansform Ph3 1차 평가변수 실패 여파, 7/27 실적 앞 불안</t>
+          <t>CARDIO-TTRansform 임상3상 1차 평가변수 실패 여파, 7/27 실적 앞 불안</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>6/29 EU CHMP 다토포타마브 승인 권고+I-DXd FDA 우선심사 모멘텀</t>
+          <t>6/29 EU 다토포타마브 승인권고+I-DXd FDA 우선심사 모멘텀</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>SCFI 4년래 신고가·중동 지정학 리스크로 아시아 역내 운임 반등 수혜</t>
+          <t>SITC(아시아 역내 컨테이너 해운): 컨테이너 운임 4년래 고점·중동 리스크로 역내 운임 반등 수혜</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>유럽 폭염으로 에어컨 수출 폭증(서유럽 +70%), 지속 자사주 매입 지지</t>
+          <t>메이디그룹(종합가전 세계 1위): 유럽 폭염 에어컨 수출 급증(서유럽 +70%)·자사주 매입 지지</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>2Q 순이익 환비 하락(-6~30%)+美 메모리주 급락 연동, 신저가 후 반등</t>
+          <t>더밍리(메모리 저장모듈): 2분기 순이익 전분기比 감소(-6~30%)+美 메모리주 급락 연동, 신저가 후 반등</t>
         </is>
       </c>
     </row>
@@ -10017,7 +10017,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>리튬가격 지속 하락·기관 중간보고 확정 매도로 신저가 후 단기 반등</t>
+          <t>톈치리튬(리튬 채굴·가공): 리튬가격 지속 하락·기관 확정매도로 신저가 후 반등</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>1Q 순이익 -47% YoY·5G사이클 조정·AI 수익화 지연, 신저가 후 반등</t>
+          <t>ZTE 중싱통신(통신장비): 1분기 순이익 -47% YoY·5G사이클 조정으로 신저가 후 반등</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>6월 80억 위안 정증 발행 계획 희석 우려로 신저가 후 기술적 반등</t>
+          <t>셰촹데이터(데이터 저장장치·IDC장비): 6월 80억위안 유상증자 계획 희석우려로 신저가 후 반등</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>H1 순이익 +50~60% 예증·7/17 자사주 매입으로 하한가 후 낙폭 회복</t>
+          <t>중톈테크(광통신 케이블): 상반기 순이익 +50~60% 예증·7/17 자사주매입으로 하한가 후 낙폭회복</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>AI算力·신화삼 매출급증+상반기 순이익 83~123% 증가 예고로 연속 涨停</t>
+          <t>쯔광구펀(H3C 서버·네트워크장비): AI연산 수요·H3C 매출급증+상반기 순이익 83~123% 증가 예고로 연속 상한가</t>
         </is>
       </c>
     </row>
@@ -11547,7 +11547,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>이구환신 정책 수혜·글로벌 가전 판매 견조로 섹터 상승 동반 신고가</t>
+          <t>하이얼스마트홈(종합가전): 이구환신(가전 교체보조) 정책 수혜·글로벌 판매 견조로 신고가</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>상반기 발전량 동비 +4.14%·홍수기 호조로 수력발전주 신고가</t>
+          <t>화능란창장수전(윈난 수력발전): 상반기 발전량 +4.14%·홍수기 호조로 신고가</t>
         </is>
       </c>
     </row>
@@ -11653,7 +11653,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>7/20 상반기 업적예증(컨테이너 처리량 +6.2% YoY) 반영 신고가</t>
+          <t>상하이항만그룹(상하이항 운영): 7/20 상반기 예증(컨테이너 물동량 +6.2% YoY) 반영 신고가</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>1Q 실적 안정·채널개혁 성과 기대감으로 섹터 수급 주도 신고가</t>
+          <t>그리전기(에어컨 대표주): 1분기 실적 안정·채널개혁 기대로 섹터 수급 신고가</t>
         </is>
       </c>
     </row>

--- a/신고신저가_20260721.xlsx
+++ b/신고신저가_20260721.xlsx
@@ -6750,7 +6750,7 @@
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>TopBuild $170억 인수완료 30% 희석+주택착공허가 2.4% 감소로 신저가</t>
+          <t>QXO(건자재 유통): TopBuild $170억 인수완료 30% 희석+주택착공허가 2.4% 감소로 신저가</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>UBS 분사 후 중립(목표 $231) 개시로 기대 미달, -4%대 급락</t>
+          <t>하니웰 에어로스페이스(항공우주 부품 분사): UBS 중립(목표 $231) 개시로 기대 미달, -4%대 급락</t>
         </is>
       </c>
     </row>
@@ -6854,7 +6854,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>캘리포니아 판사, 파라마운트·스카이댄스 $1100억 딜 8/3까지 중단 명령</t>
+          <t>워너브라더스 디스커버리(미디어·스트리밍): 파라마운트·스카이댄스 $1100억 딜 8/3까지 법원 중단명령</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>용접장비 수요 부진·고밸류 부담 지속, 7/30 실적 앞 관망 신저가</t>
+          <t>링컨일렉트릭(산업용 용접장비): 수요 부진·고밸류 부담, 7/30 실적 앞 관망 신저가</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>CARDIO-TTRansform 임상3상 1차 평가변수 실패 여파, 7/27 실적 앞 불안</t>
+          <t>아스트라제네카(글로벌 제약): CARDIO-TTRansform 임상3상 1차 평가변수 실패 여파, 7/27 실적 앞 불안</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>바클레이즈 목표가 $21→$23 상향+트루이스트 매수 재확인, 원유 인프라 수급 호조</t>
+          <t>플레인스올아메리칸(원유·NGL 파이프라인 MLP): 바클레이즈 목표가 $21→$23 상향+트루이스트 매수 재확인</t>
         </is>
       </c>
     </row>
@@ -7588,7 +7588,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>7/15 분기배당($0.176) 선언+재생에너지 확장 모멘텀, 7/30 실적 기대</t>
+          <t>AES(글로벌 발전·재생에너지 유틸리티): 7/15 분기배당 선언+재생에너지 확장, 7/30 실적 기대</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>창업자 맥킴 회장 퇴임·신임 의장 취임 거버넌스 전환 속 신고가 지속</t>
+          <t>클린하버스(산업폐기물·환경서비스): 창업자 회장 퇴임 거버넌스 전환 속 신고가 지속</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>S&amp;P400 편입(7/17)+UBS·BTIG·BofA 목표가 상향, 신고가 후 소폭 조정</t>
+          <t>브라이트스프링(재택·전문약국 헬스케어): S&amp;P400 편입(7/17)+증권사 목표가 상향, 신고가 후 소폭 조정</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>시민증권 목표가 $100→$120 상향 불구 시장 전반 차익실현 매도</t>
+          <t>리버티 포뮬러원(F1 미디어·중계권): 목표가 $100→$120 상향 불구 시장 전반 차익실현 매도</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>보험섹터 상위·소폼포 690억엔 자사주매입 지속으로 수급 개선</t>
+          <t>손포홀딩스(손해보험 지주): 보험섹터 강세·690억엔 자사주매입 지속으로 수급 개선</t>
         </is>
       </c>
     </row>
@@ -8969,7 +8969,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>US스틸 철강가 호조·FY27 이익 1000억엔 기여 기대로 자율반등</t>
+          <t>닛폰스틸(일본 최대 철강): US스틸 철강가 호조·FY27 이익 1000억엔 기여 기대로 자율반등</t>
         </is>
       </c>
     </row>
@@ -9020,7 +9020,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>7/2 인실리코 AI 신약발굴 딜(~$600M) 재료+7/30 결산 앞둔 매수</t>
+          <t>다케다약품(일본 최대 제약): 7/2 인실리코 AI 신약발굴 딜(~$600M)+7/30 결산 앞둔 매수</t>
         </is>
       </c>
     </row>
@@ -9073,7 +9073,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>광범위 자율반등+7/27 결산 앞둔 매수, 통기 순익 소폭 증가 예상</t>
+          <t>캐논(카메라·사무기기·반도체 노광): 광범위 자율반등+7/27 결산 앞둔 매수</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>6/29 EU 다토포타마브 승인권고+I-DXd FDA 우선심사 모멘텀</t>
+          <t>다이이치산쿄(제약, ADC 항암 강자): 6/29 EU 다토포타마브 승인권고+I-DXd FDA 우선심사 모멘텀</t>
         </is>
       </c>
     </row>

--- a/신고신저가_20260721.xlsx
+++ b/신고신저가_20260721.xlsx
@@ -3468,67 +3468,67 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XLE US</t>
+          <t>XLB US</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>소재</t>
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>2.1</v>
+        <v>-1.1</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>6.7</v>
+        <v>-3.5</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>6.1</v>
+        <v>-3.2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>31.4</v>
+        <v>11.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>5.6</v>
+        <v>0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>-0.6</v>
+        <v>12.5</v>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>64.3</v>
+        <v>-12.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R2" s="6" t="n">
-        <v>53.3</v>
+        <v>27.4</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T2" s="6" t="n">
-        <v>-32.7</v>
+        <v>20.5</v>
       </c>
       <c r="U2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -3539,67 +3539,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XLK US</t>
+          <t>XLV US</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>테크</t>
+          <t>헬스케어</t>
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.1</v>
+        <v>-1.1</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>-3.1</v>
+        <v>-1.3</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>-5.3</v>
+        <v>6.1</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>14</v>
+        <v>7.5</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>22.3</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>24.6</v>
+        <v>14.5</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>21.6</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" s="6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="U3" t="n">
         <v>5</v>
-      </c>
-      <c r="N3" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v>-27.7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>9</v>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4</v>
-      </c>
-      <c r="T3" s="6" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3610,67 +3610,67 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XLC US</t>
+          <t>XLE US</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>커뮤니케이션</t>
+          <t>에너지</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>-0.7</v>
+        <v>2.1</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1.7</v>
+        <v>6.7</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-6.7</v>
+        <v>6.1</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-5.3</v>
+        <v>31.4</v>
       </c>
       <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>9</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>-32.7</v>
+      </c>
+      <c r="U4" t="n">
         <v>11</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="6" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v>-37.6</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>11</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="S4" t="n">
-        <v>11</v>
-      </c>
-      <c r="T4" s="6" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XLRE US</t>
+          <t>XLK US</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>리츠</t>
+          <t>테크</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1.2</v>
+        <v>-3.1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>3.8</v>
+        <v>-5.3</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>2.6</v>
+        <v>14</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>13.8</v>
+        <v>22.3</v>
       </c>
       <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>-27.7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>9</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>9</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>-26.2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>8</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
       <c r="T5" s="6" t="n">
-        <v>-2.2</v>
+        <v>43.6</v>
       </c>
       <c r="U5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3752,67 +3752,67 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XLP US</t>
+          <t>XLC US</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>필수소비재</t>
+          <t>커뮤니케이션</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>3.6</v>
+        <v>-6.7</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>10.6</v>
+        <v>-5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1.5</v>
+        <v>23.1</v>
       </c>
       <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>-37.6</v>
+      </c>
+      <c r="Q6" t="n">
         <v>11</v>
       </c>
-      <c r="L6" s="6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>7</v>
-      </c>
-      <c r="N6" s="6" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>10</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="R6" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="U6" t="n">
         <v>3</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" s="6" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -3823,67 +3823,67 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XLF US</t>
+          <t>XLRE US</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>리츠</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
         <v>-0.4</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0.1</v>
+        <v>1.2</v>
       </c>
       <c r="F7" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="J7" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M7" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="N7" s="6" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>-26.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>8</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="N7" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="O7" t="n">
-        <v>7</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>-10.6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
       <c r="T7" s="6" t="n">
-        <v>-1.7</v>
+        <v>-2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -3894,67 +3894,67 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XLU US</t>
+          <t>XLP US</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>유틸리티</t>
+          <t>필수소비재</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-1.7</v>
+        <v>0.3</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-2</v>
+        <v>3.6</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>6.7</v>
+        <v>10.6</v>
       </c>
       <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="M8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>4</v>
-      </c>
       <c r="N8" s="6" t="n">
-        <v>-7.2</v>
+        <v>-0.8</v>
       </c>
       <c r="O8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>17.7</v>
+        <v>17.2</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" s="6" t="n">
-        <v>0.5</v>
+        <v>10.1</v>
       </c>
       <c r="U8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -3965,67 +3965,67 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XLI US</t>
+          <t>XLF US</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>산업재</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>-0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-1.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.6</v>
+        <v>4</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2.9</v>
+        <v>7.3</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>15.4</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="O9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8</v>
-      </c>
       <c r="T9" s="6" t="n">
-        <v>10.9</v>
+        <v>-1.7</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -4036,67 +4036,67 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XLY US</t>
+          <t>XLU US</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>경기소비재</t>
+          <t>유틸리티</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>-1.2</v>
+        <v>-1.7</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.6</v>
+        <v>1.7</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-4.6</v>
+        <v>-2</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-3.6</v>
+        <v>6.7</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>11</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="S10" t="n">
         <v>9</v>
       </c>
-      <c r="L10" s="6" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>-36.3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>10</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
       <c r="T10" s="6" t="n">
-        <v>29.6</v>
+        <v>0.5</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -4107,67 +4107,67 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XLB US</t>
+          <t>XLI US</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>소재</t>
+          <t>산업재</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-3.5</v>
+        <v>-0.6</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-3.2</v>
+        <v>2.9</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>11.2</v>
+        <v>15.4</v>
       </c>
       <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="Q11" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>7</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>11</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>5</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>-12.3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>7</v>
-      </c>
       <c r="R11" s="6" t="n">
-        <v>27.4</v>
+        <v>21.1</v>
       </c>
       <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" s="6" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="U11" t="n">
         <v>6</v>
-      </c>
-      <c r="T11" s="6" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -4178,67 +4178,67 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XLV US</t>
+          <t>XLY US</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>헬스케어</t>
+          <t>경기소비재</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>-1.1</v>
+        <v>-0.7</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>6.1</v>
+        <v>-0.6</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7.5</v>
+        <v>-4.6</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>3.8</v>
+        <v>-3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>2.5</v>
+        <v>26.5</v>
       </c>
       <c r="M12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>-36.3</v>
+      </c>
+      <c r="Q12" t="n">
         <v>10</v>
       </c>
-      <c r="N12" s="6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>8</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
       <c r="R12" s="6" t="n">
-        <v>26</v>
+        <v>27.9</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>13.3</v>
+        <v>29.6</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6083,67 +6083,67 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>512880 CH</t>
+          <t>512690 CH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>증권</t>
+          <t>백주(주류)</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>-0.4</v>
+        <v>-1.6</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-1.5</v>
+        <v>4.4</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>3.5</v>
+        <v>-12.4</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-8</v>
+        <v>-20.7</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>3.5</v>
+        <v>-13</v>
       </c>
       <c r="K39" t="n">
+        <v>10</v>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="M39" t="n">
         <v>8</v>
       </c>
-      <c r="L39" s="6" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="M39" t="n">
+      <c r="N39" s="6" t="n">
+        <v>-18.6</v>
+      </c>
+      <c r="O39" t="n">
+        <v>8</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="Q39" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v>-26.1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>5</v>
-      </c>
       <c r="R39" s="6" t="n">
-        <v>-3.8</v>
+        <v>-3</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T39" s="6" t="n">
-        <v>17.5</v>
+        <v>302.8</v>
       </c>
       <c r="U39" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -6154,68 +6154,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>512010 CH</t>
+          <t>512800 CH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>의약</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="I40" t="n">
-        <v>4</v>
-      </c>
-      <c r="J40" s="6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K40" t="n">
-        <v>7</v>
-      </c>
-      <c r="L40" s="6" t="n">
-        <v>-12.2</v>
-      </c>
-      <c r="M40" t="n">
-        <v>9</v>
-      </c>
-      <c r="N40" s="6" t="n">
-        <v>-14</v>
-      </c>
-      <c r="O40" t="n">
-        <v>6</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v>-24.5</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4</v>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v>-15.7</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" s="6" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>4</v>
-      </c>
+          <t>은행</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" s="6" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" s="6" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" s="6" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" s="6" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" s="6" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6225,68 +6189,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>159928 CH</t>
+          <t>512400 CH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>소비(消费)</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="I41" t="n">
-        <v>6</v>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="K41" t="n">
-        <v>9</v>
-      </c>
-      <c r="L41" s="6" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="M41" t="n">
-        <v>7</v>
-      </c>
-      <c r="N41" s="6" t="n">
-        <v>-18.3</v>
-      </c>
-      <c r="O41" t="n">
-        <v>7</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v>-13.4</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2</v>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="S41" t="n">
-        <v>9</v>
-      </c>
-      <c r="T41" s="6" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="U41" t="n">
-        <v>2</v>
-      </c>
+          <t>유색금속</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr"/>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" s="6" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" s="6" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" s="6" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" s="6" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" s="6" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6296,68 +6224,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>512690 CH</t>
+          <t>512200 CH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>백주(주류)</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="E42" s="6" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G42" s="6" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>-20.7</v>
-      </c>
-      <c r="I42" t="n">
-        <v>9</v>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>-13</v>
-      </c>
-      <c r="K42" t="n">
-        <v>10</v>
-      </c>
-      <c r="L42" s="6" t="n">
-        <v>-11</v>
-      </c>
-      <c r="M42" t="n">
-        <v>8</v>
-      </c>
-      <c r="N42" s="6" t="n">
-        <v>-18.6</v>
-      </c>
-      <c r="O42" t="n">
-        <v>8</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="S42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T42" s="6" t="n">
-        <v>302.8</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1</v>
-      </c>
+          <t>부동산</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" s="6" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" s="6" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" s="6" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" s="6" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" s="6" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6367,32 +6259,68 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>512800 CH</t>
+          <t>512880 CH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>은행</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="6" t="inlineStr"/>
-      <c r="F43" s="6" t="inlineStr"/>
-      <c r="G43" s="6" t="inlineStr"/>
-      <c r="H43" s="6" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" s="6" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" s="6" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" s="6" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" s="6" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" s="6" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+          <t>증권</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>8</v>
+      </c>
+      <c r="L43" s="6" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="S43" t="n">
+        <v>8</v>
+      </c>
+      <c r="T43" s="6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="U43" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6402,32 +6330,68 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>512400 CH</t>
+          <t>512010 CH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>유색금속</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr"/>
-      <c r="E44" s="6" t="inlineStr"/>
-      <c r="F44" s="6" t="inlineStr"/>
-      <c r="G44" s="6" t="inlineStr"/>
-      <c r="H44" s="6" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" s="6" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" s="6" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" s="6" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" s="6" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" s="6" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" s="6" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+          <t>의약</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K44" t="n">
+        <v>7</v>
+      </c>
+      <c r="L44" s="6" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>9</v>
+      </c>
+      <c r="N44" s="6" t="n">
+        <v>-14</v>
+      </c>
+      <c r="O44" t="n">
+        <v>6</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4</v>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" s="6" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6437,37 +6401,73 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>512200 CH</t>
+          <t>159928 CH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>부동산</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr"/>
-      <c r="E45" s="6" t="inlineStr"/>
-      <c r="F45" s="6" t="inlineStr"/>
-      <c r="G45" s="6" t="inlineStr"/>
-      <c r="H45" s="6" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" s="6" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" s="6" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" s="6" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" s="6" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" s="6" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" s="6" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+          <t>소비(消费)</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>6</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="K45" t="n">
+        <v>9</v>
+      </c>
+      <c r="L45" s="6" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>7</v>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="O45" t="n">
+        <v>7</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="S45" t="n">
+        <v>9</v>
+      </c>
+      <c r="T45" s="6" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>※ 미국=SPDR 섹터 ETF, 일본=TOPIX-17 섹터 ETF(1617~1633), 중국A=주요 섹터 ETF(상해·심천) · 홍콩은 섹터 ETF가 얇아 시장·테크 대표만 · 수익률은 배당 포함 총수익 기준(미국=야후 수정주가, 중·홍=eastmoney 전복권) — 블룸버그 가격수익률과 고배당 섹터에서 연 1~2%p 차이 가능 · 시장 내 1D 내림차순</t>
+          <t>※ 미국=SPDR 섹터 ETF, 일본=TOPIX-17 섹터 ETF(1617~1633), 중국A=주요 섹터 ETF(상해·심천) · 홍콩은 섹터 ETF가 얇아 시장·테크 대표만 · 수익률은 배당 포함 총수익 기준(미국=야후 수정주가, 중·홍=eastmoney 전복권) — 블룸버그 가격수익률과 고배당 섹터에서 연 1~2%p 차이 가능 · 시장별 1D 변동 1%↑는 위(상승→하락순)·1% 미만 보합은 아래로</t>
         </is>
       </c>
     </row>

--- a/신고신저가_20260721.xlsx
+++ b/신고신저가_20260721.xlsx
@@ -1010,31 +1010,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Commercial Services</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-1</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>36</v>
+        <v>10.6</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="11">
@@ -1045,31 +1045,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-1</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>21</v>
+        <v>23.8</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="12">
@@ -1080,31 +1080,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Consumer Non-Durables</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>혼조</t>
+        <v>-1</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>22.6</v>
+        <v>33.2</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="13">
@@ -1115,31 +1115,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Distribution Services</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>혼조</t>
+        <v>-1</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>24.2</v>
+        <v>25.4</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="14">
@@ -1150,31 +1150,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-2</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>55.6</v>
+        <v>43.9</v>
       </c>
       <c r="I14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="15">
@@ -1185,20 +1185,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.6</v>
+        <v>29.6</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="16">
@@ -1220,20 +1220,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.8</v>
+        <v>22.6</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="17">
@@ -1255,31 +1255,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>33.2</v>
+        <v>36</v>
       </c>
       <c r="I17" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="18">
@@ -1290,31 +1290,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>25.4</v>
+        <v>21</v>
       </c>
       <c r="I18" t="n">
-        <v>7.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="19">
@@ -1325,31 +1325,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>혼조</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="I19" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1360,31 +1360,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Distribution Services</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>혼조</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>29.6</v>
+        <v>24.2</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="21">
@@ -1395,31 +1395,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>22.6</v>
+        <v>55.6</v>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2130,31 +2130,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Commercial Services</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-2</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10.4</v>
+        <v>90.3</v>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="43">
@@ -2165,31 +2165,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-2</v>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>12.4</v>
+        <v>21.6</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="44">
@@ -2200,11 +2200,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Consumer Non-Durables</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>15.1</v>
+        <v>10.4</v>
       </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="45">
@@ -2235,11 +2235,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>15.6</v>
+        <v>12.4</v>
       </c>
       <c r="I45" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="46">
@@ -2270,11 +2270,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Distribution Services</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>11.4</v>
+        <v>15.1</v>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="47">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Energy Minerals</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>11.4</v>
+        <v>15.6</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="48">
@@ -2340,11 +2340,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Distribution Services</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>7.6</v>
+        <v>11.4</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="49">
@@ -2375,11 +2375,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Energy Minerals</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>34.1</v>
+        <v>11.4</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="50">
@@ -2410,11 +2410,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="51">
@@ -2445,11 +2445,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>13.3</v>
+        <v>34.1</v>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -2480,11 +2480,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>24.9</v>
+        <v>3.9</v>
       </c>
       <c r="I52" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="53">
@@ -2515,11 +2515,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>20.9</v>
+        <v>13.3</v>
       </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="54">
@@ -2550,11 +2550,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>17.1</v>
+        <v>24.9</v>
       </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="55">
@@ -2585,11 +2585,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>14.3</v>
+        <v>20.9</v>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="56">
@@ -2620,31 +2620,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>90.3</v>
+        <v>17.1</v>
       </c>
       <c r="I56" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="57">
@@ -2655,31 +2655,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>21.6</v>
+        <v>14.3</v>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="58">
@@ -2830,31 +2830,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Consumer Non-Durables</t>
+          <t>Commercial Services</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>19.2</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="63">
@@ -2865,31 +2863,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Distribution Services</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-1</v>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>25.4</v>
+        <v>16.5</v>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="64">
@@ -2900,7 +2898,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Energy Minerals</t>
+          <t>Industrial Services</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2910,21 +2908,21 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-1</v>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>14.3</v>
+        <v>7.5</v>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="65">
@@ -2935,31 +2933,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Health Services</t>
+          <t>Technology Services</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-2</v>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>24.1</v>
+        <v>51.3</v>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="66">
@@ -2970,31 +2968,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Health Technology</t>
+          <t>Non-Energy Minerals</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-3</v>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>45</v>
+        <v>16.4</v>
       </c>
       <c r="I66" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="67">
@@ -3005,29 +3003,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Process Industries</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>약세</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>25.2</v>
+      </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -3038,29 +3038,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Commercial Services</t>
+          <t>Producer Manufacturing</t>
         </is>
       </c>
       <c r="C68" t="n">
+        <v>43</v>
+      </c>
+      <c r="D68" t="n">
         <v>1</v>
       </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F68" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>39</v>
+      </c>
       <c r="I68" t="n">
-        <v>15.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="69">
@@ -3071,20 +3073,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Communications</t>
+          <t>Electronic Technology</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F69" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
@@ -3092,10 +3094,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>16.5</v>
+        <v>70.2</v>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="70">
@@ -3106,31 +3108,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Industrial Services</t>
+          <t>Consumer Non-Durables</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>7.5</v>
+        <v>19.2</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="71">
@@ -3141,31 +3143,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Technology Services</t>
+          <t>Distribution Services</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>51.3</v>
+        <v>25.4</v>
       </c>
       <c r="I71" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="72">
@@ -3176,31 +3178,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Non-Energy Minerals</t>
+          <t>Energy Minerals</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>16.4</v>
+        <v>14.3</v>
       </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="73">
@@ -3211,31 +3213,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Process Industries</t>
+          <t>Health Services</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>25.2</v>
+        <v>24.1</v>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="74">
@@ -3246,31 +3248,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Producer Manufacturing</t>
+          <t>Health Technology</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
+        <v>0</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I74" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="75">
@@ -3281,31 +3283,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Electronic Technology</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>-10</v>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>약세</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>70.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
-        <v>11.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="77">

--- a/신고신저가_20260721.xlsx
+++ b/신고신저가_20260721.xlsx
@@ -75,13 +75,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -3327,30 +3330,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3371,90 +3375,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -3476,58 +3485,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>섹터 내 최약(-1.0%). 비에너지 광물·금속 신저 다발(순강도-2). 주간·1개월도 마이너스로 약세 지속.</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="n">
         <v>-1</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="7" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="7" t="n">
         <v>-3.5</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="7" t="n">
         <v>-3.2</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="7" t="n">
         <v>11.2</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="7" t="n">
         <v>9.9</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>7</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>11</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="7" t="n">
         <v>12.5</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>5</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="7" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>7</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="7" t="n">
         <v>27.4</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>6</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="7" t="n">
         <v>20.5</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3547,58 +3561,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>약세(-1.1%). 제약·바이오 52주 신저 다발(순강도-2), AZN 임상3상 1차변수 실패(-2.6%)로 투심 악화. 서비스는 상대 견조.</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="7" t="n">
         <v>6.1</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="7" t="n">
         <v>7.5</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="7" t="n">
         <v>3.8</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>8</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="7" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="7" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="7" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="7" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3618,58 +3637,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>강세(+0.5%). 에너지광물 신고 4개(순강도+4), 원유 인프라 PAA(파이프라인) 신고가 — 시장 약세 속 상대 강세.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>2.1</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>6.7</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>6.1</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>31.4</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="7" t="n">
         <v>7.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>8</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="7" t="n">
         <v>5.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>8</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="7" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>9</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="7" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="7" t="n">
         <v>53.3</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="7" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -3689,58 +3713,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>보합(+0.1%). SW·IT서비스는 신고 우위(순강도+2), 반도체·전자하드웨어는 신저 다발(-2)로 내부 혼조. 주간 -3.1%.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>-3.1</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>-5.3</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>22.3</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="7" t="n">
         <v>24.6</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="7" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>5</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="7" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>9</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="7" t="n">
         <v>34.7</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>4</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="7" t="n">
         <v>43.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3760,58 +3789,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>보합(+0.1%). WBD -3.8%(파라마운트·스카이댄스 딜 법원 중단명령) 등 미디어 신저로 섹터 순강도 약세(-1).</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>1.7</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>-6.7</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>-5.3</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="7" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="7" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="7" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="7" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="7" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3831,58 +3865,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>소폭 조정(-0.4%). 금리 민감 방어섹터, 개별 신고/신저 신호 미미 — 특별 촉매 없음.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>1.2</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>3.8</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>2.6</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>13.8</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="7" t="n">
         <v>2.6</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>10</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="7" t="n">
         <v>5.1</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>9</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="7" t="n">
         <v>12.4</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>6</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="7" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>8</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="7" t="n">
         <v>46.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>2</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="7" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3902,58 +3941,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>소폭 하락(-0.4%). 순강도 무신호(혼조) — 뚜렷한 촉매 없이 방어적 흐름.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <v>2.1</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>3.6</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="7" t="n">
         <v>10.6</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="7" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="7" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="7" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3973,58 +4017,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>ETF는 소폭 하락(-0.4%)이나 은행·보험 신고가 6개로 시장 내 최다(순강도+6) — 개별 강세 지속, 방어 우위.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="7" t="n">
         <v>7.3</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="7" t="n">
         <v>3.2</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>9</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="7" t="n">
         <v>14.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>5</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="7" t="n">
         <v>30.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>2</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>7</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="7" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>6</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="7" t="n">
         <v>34.8</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="7" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4044,58 +4093,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>ETF 소폭 하락(-0.5%)이나 신고가 3개(순강도+3), AES 등 배당·재생에너지 개별 강세 — 방어 수요.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <v>1.7</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="7" t="n">
         <v>-2</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="7" t="n">
         <v>6.7</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>7</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="7" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="7" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="7" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="7" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4115,58 +4169,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>약세(-0.7%). 자본재 신저, 링컨일렉트릭(용접) -2.9%·하니웰에어로 -4.3%. 운송·산업서비스는 신고로 혼재.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>2.9</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>15.4</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="7" t="n">
         <v>19.3</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="7" t="n">
         <v>17.3</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>6</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="7" t="n">
         <v>18.1</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>4</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="7" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>5</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="7" t="n">
         <v>21.1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>8</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="7" t="n">
         <v>10.9</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4186,58 +4245,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>약세(-0.7%). 소비서비스·소매 신저(각 순강도-1), 내구재는 무신호. 경기민감 소비 상대 부진.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>-4.6</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>-3.6</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>10</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="7" t="n">
         <v>7.4</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>9</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="7" t="n">
         <v>26.5</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>3</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="7" t="n">
         <v>39.6</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>3</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="7" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>10</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="7" t="n">
         <v>27.9</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="7" t="n">
         <v>29.6</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4257,58 +4321,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="7" t="n">
         <v>4.6</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="7" t="n">
         <v>-5.2</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="7" t="n">
         <v>-3.9</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="7" t="n">
         <v>31.1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="7" t="n">
         <v>22.3</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>5</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="7" t="n">
         <v>33.9</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>6</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="7" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>15</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="7" t="n">
         <v>7.5</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>9</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="7" t="n">
         <v>17.7</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4328,58 +4393,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="7" t="n">
         <v>4.5</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>4.1</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>2.9</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="7" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="7" t="n">
         <v>14.3</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>8</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="7" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="7" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="7" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="7" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="7" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="7" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4399,58 +4465,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="7" t="n">
         <v>3.9</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <v>2.9</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="7" t="n">
         <v>6.3</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="7" t="n">
         <v>13.7</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="7" t="n">
         <v>28.9</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="7" t="n">
         <v>21.4</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>10</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>2</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="7" t="n">
         <v>27.2</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>10</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="7" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>6</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="7" t="n">
         <v>22.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>6</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="7" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4470,58 +4537,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="7" t="n">
         <v>3.1</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>3.3</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="7" t="n">
         <v>2.1</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="7" t="n">
         <v>-8.9</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>15</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="7" t="n">
         <v>37.4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>7</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="7" t="n">
         <v>6.3</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>15</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>4</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="7" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>7</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="7" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>16</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="7" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4541,58 +4609,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="7" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="7" t="n">
         <v>6.1</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="7" t="n">
         <v>18.8</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="7" t="n">
         <v>44.1</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="7" t="n">
         <v>44.8</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="7" t="n">
         <v>50.4</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="7" t="n">
         <v>33.2</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>8</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="7" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="7" t="n">
         <v>26.7</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="7" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4612,58 +4681,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="7" t="n">
         <v>2.8</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <v>-3.7</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="7" t="n">
         <v>-22.5</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="7" t="n">
         <v>-17.2</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="7" t="n">
         <v>35.9</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="7" t="n">
         <v>68.8</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="7" t="n">
         <v>20.6</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>8</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>4</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="7" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>5</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="7" t="n">
         <v>20.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>7</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="7" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4683,58 +4753,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="7" t="n">
         <v>-7.7</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="7" t="n">
         <v>13.1</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>9</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="7" t="n">
         <v>41.5</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>5</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="7" t="n">
         <v>20.1</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>9</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>1</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="7" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>3</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="7" t="n">
         <v>29.2</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="7" t="n">
         <v>1.9</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4754,58 +4825,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="7" t="n">
         <v>1.8</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>-3.8</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="7" t="n">
         <v>-10.1</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="7" t="n">
         <v>12.5</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="7" t="n">
         <v>30.2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="7" t="n">
         <v>27.5</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>9</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="7" t="n">
         <v>17.9</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>10</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="7" t="n">
         <v>33.7</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>7</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="7" t="n">
         <v>-23</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>17</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>5</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="7" t="n">
         <v>26.2</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4825,58 +4897,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="7" t="n">
         <v>1.7</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>2.8</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <v>6.2</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="7" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>16</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="7" t="n">
         <v>41.6</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>4</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="7" t="n">
         <v>13.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>12</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="7" t="n">
         <v>23.6</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>11</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="7" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>11</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="7" t="n">
         <v>6.8</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>10</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="7" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4896,58 +4969,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>4.2</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <v>6.3</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="7" t="n">
         <v>-4.2</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="7" t="n">
         <v>-4.7</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>17</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="7" t="n">
         <v>13.5</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>14</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="7" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>11</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="7" t="n">
         <v>40.5</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>2</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="7" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>16</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="7" t="n">
         <v>27.8</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4967,58 +5041,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="7" t="n">
         <v>1.1</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="7" t="n">
         <v>3.1</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="7" t="n">
         <v>10.8</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="7" t="n">
         <v>5.7</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>11</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="7" t="n">
         <v>13.9</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>13</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>7</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="7" t="n">
         <v>17.9</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>15</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="7" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>13</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>13</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="7" t="n">
         <v>21.9</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5038,58 +5113,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="7" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="7" t="n">
         <v>-5.5</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="7" t="n">
         <v>10.4</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>10</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>3</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="7" t="n">
         <v>21.6</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>6</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>9</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="7" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>12</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="7" t="n">
         <v>12.6</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>8</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="7" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5109,58 +5185,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="7" t="n">
         <v>2.6</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="7" t="n">
         <v>7.2</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="7" t="n">
         <v>-6.1</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="7" t="n">
         <v>2.9</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>14</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="7" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>16</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="7" t="n">
         <v>10.8</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>13</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>17</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="7" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>4</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="7" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>17</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="7" t="n">
         <v>4.6</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5180,58 +5257,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>3.2</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>13</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="7" t="n">
         <v>19.9</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>11</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>17</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>14</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="7" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>8</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="7" t="n">
         <v>4.7</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>12</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="7" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5251,58 +5329,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="7" t="n">
         <v>1.1</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="7" t="n">
         <v>4.1</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="7" t="n">
         <v>6.7</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="7" t="n">
         <v>16.6</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>7</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="7" t="n">
         <v>11.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>15</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>14</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="7" t="n">
         <v>22.3</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>13</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="7" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>10</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="7" t="n">
         <v>5.6</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>11</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="7" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5322,58 +5401,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="7" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="7" t="n">
         <v>6.6</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="7" t="n">
         <v>24.2</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>5</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="7" t="n">
         <v>8.6</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>17</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="7" t="n">
         <v>3.9</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>16</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="7" t="n">
         <v>23.1</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>12</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="7" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>14</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="7" t="n">
         <v>2.1</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>14</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="7" t="n">
         <v>8.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5393,58 +5473,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="7" t="n">
         <v>0.1</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="7" t="n">
         <v>0.9</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="7" t="n">
         <v>4.7</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="7" t="n">
         <v>1.9</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="7" t="n">
         <v>4.4</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>12</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="7" t="n">
         <v>16.8</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>12</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="7" t="n">
         <v>23.4</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>4</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="7" t="n">
         <v>16.4</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>16</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="7" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>9</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="7" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>15</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="7" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5464,56 +5545,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="7" t="n">
         <v>1.2</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>2.3</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="7" t="n">
         <v>4.3</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="7" t="n">
         <v>-4.7</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="7" t="n">
         <v>-12.7</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>3</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="7" t="n">
         <v>22.7</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="7" t="n">
         <v>18.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="7" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="7" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>3</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="7" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>3</v>
       </c>
-      <c r="T30" s="6" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" s="7" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5531,58 +5613,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="7" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>2.9</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="7" t="n">
         <v>5.3</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="7" t="n">
         <v>-2.6</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="7" t="n">
         <v>-0.3</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="7" t="n">
         <v>32.8</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="7" t="n">
         <v>24.8</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>2</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="7" t="n">
         <v>-11.9</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>2</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="7" t="n">
         <v>-14.4</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>1</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="7" t="n">
         <v>-13.5</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>1</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="7" t="n">
         <v>-1.2</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5602,58 +5685,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="7" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>2.9</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="7" t="n">
         <v>5.2</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="7" t="n">
         <v>-4.4</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="7" t="n">
         <v>-5.2</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="7" t="n">
         <v>26.2</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>2</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="7" t="n">
         <v>32.1</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="7" t="n">
         <v>-12.8</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>3</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="7" t="n">
         <v>-17.8</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>2</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="7" t="n">
         <v>-23.6</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>2</v>
       </c>
-      <c r="T32" s="6" t="n">
+      <c r="U32" s="7" t="n">
         <v>-2</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5673,58 +5757,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>급반등(+9.0%, 전주 -13.3% 낙폭 되돌림). 단 개별종목은 52주 신저 다발(전자기술 순강도-10) — 지수 반등과 종목 약세 괴리, 기술적 성격.</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="7" t="n">
         <v>-13.3</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="7" t="n">
         <v>-11.1</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="7" t="n">
         <v>39.3</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="7" t="n">
         <v>54.9</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>4</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="7" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>2</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="7" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="7" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>9</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="7" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>3</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="7" t="n">
         <v>46.2</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5744,58 +5833,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>급반등(+6.6%, 전주 -10.7%). AI·성장주 저가매수 유입. 신저 다발 지속돼 낙폭과대 되돌림 성격.</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="n">
         <v>6.6</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="7" t="n">
         <v>-10.7</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="7" t="n">
         <v>-15</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="7" t="n">
         <v>20.4</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="7" t="n">
         <v>36.4</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="7" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>3</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>4</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="7" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>8</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="7" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>6</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5815,58 +5909,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>반등(+6.2%, 전주 -12.5%). ZTE(중싱통신) 등 개별은 신저 후 반등, 통신 순강도 약세(-1) 잔존.</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="n">
         <v>6.2</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="7" t="n">
         <v>-12.5</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="7" t="n">
         <v>-23.2</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="7" t="n">
         <v>12.4</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="7" t="n">
         <v>42.4</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="7" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="7" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>3</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="7" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="7" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>10</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="7" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>5</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="7" t="n">
         <v>19.3</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5886,56 +5985,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>반등(+3.0%). 다만 3개월 -22.6%로 중기 약세 지속, 톈치리튬 등 리튬 신저 — 낙폭과대 되돌림.</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="7" t="n">
         <v>-4.1</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="7" t="n">
         <v>-20.8</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="7" t="n">
         <v>-22.6</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="7" t="n">
         <v>-16.4</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>7</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="7" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>2</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>6</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="7" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>9</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="7" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>7</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="7" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="7" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5953,58 +6057,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>반등(+2.3%, 전주 -6.8%, 3개월 -22.2%). 중기 낙폭과대 되돌림, 뚜렷한 정책 촉매는 미확인.</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="n">
         <v>2.3</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="7" t="n">
         <v>-6.8</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="7" t="n">
         <v>-16.9</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="7" t="n">
         <v>-22.2</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="7" t="n">
         <v>-21.4</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>10</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="7" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>5</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>5</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="7" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>5</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="7" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>5</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="7" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>4</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="7" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6024,56 +6133,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>반등(+2.2%). 3개월 -25.1%로 섹터 최약권, 과매도 기술 반등 성격.</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="n">
         <v>2.2</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="7" t="n">
         <v>-6.1</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="7" t="n">
         <v>-23.1</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="7" t="n">
         <v>-25.1</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="7" t="n">
         <v>-16.6</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="7" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>6</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="7" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>10</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="7" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>10</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="7" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>3</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="7" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="7" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6091,58 +6205,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>약세(-1.6%). 성장주 반등장에 자금 이탈, 전주 +7.3% 되돌림.</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="7" t="n">
         <v>7.3</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="7" t="n">
         <v>4.4</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="7" t="n">
         <v>-12.4</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="7" t="n">
         <v>-20.7</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>9</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="7" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>10</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="7" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>8</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="7" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>8</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="7" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>1</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="7" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>7</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="7" t="n">
         <v>302.8</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6162,24 +6281,29 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="6" t="inlineStr"/>
-      <c r="F40" s="6" t="inlineStr"/>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" s="6" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" s="6" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" s="6" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" s="6" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" s="6" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" s="6" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 금융 순강도 +2(신고 우위)로 방어 강세 추정 — 재확인 필요.</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr"/>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" s="7" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" s="7" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" s="7" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" s="7" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6197,24 +6321,29 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="6" t="inlineStr"/>
-      <c r="F41" s="6" t="inlineStr"/>
-      <c r="G41" s="6" t="inlineStr"/>
-      <c r="H41" s="6" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" s="6" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" s="6" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" s="6" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" s="6" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" s="6" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 비에너지 광물 순강도 -3(신저 다발, 약세).</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" s="7" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" s="7" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" s="7" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" s="7" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6232,24 +6361,29 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr"/>
-      <c r="E42" s="6" t="inlineStr"/>
-      <c r="F42" s="6" t="inlineStr"/>
-      <c r="G42" s="6" t="inlineStr"/>
-      <c r="H42" s="6" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" s="6" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" s="6" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" s="6" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" s="6" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>당일 ETF 시세 수집 실패(공란). 별도 순강도 신호 미미.</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr"/>
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" s="7" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" s="7" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" s="7" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" s="7" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6267,58 +6401,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>소폭 하락(-0.4%). 은행 강세 대비 상대 부진, 거래대금 관망세.</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="7" t="n">
         <v>0.9</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="7" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="7" t="n">
         <v>-8</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>5</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>8</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="7" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="7" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="7" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>5</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="7" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>8</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="7" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6338,58 +6477,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>약세(-0.8%). 성장주 반등장에서 소외, 순강도 무신호.</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="7" t="n">
         <v>1.6</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="7" t="n">
         <v>1.9</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="7" t="n">
         <v>-1.3</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="7" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>7</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="7" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>9</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="7" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>6</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="7" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>4</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="7" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>10</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="7" t="n">
         <v>58.4</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6409,58 +6553,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>약세(-0.9%). 전주 +6.0% 되돌림, 성장주로 순환매 이탈.</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="7" t="n">
         <v>6.9</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="7" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="7" t="n">
         <v>-15.5</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>6</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="7" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>9</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="7" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>7</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="7" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>7</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="7" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>2</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="7" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>9</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="7" t="n">
         <v>72.7</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6472,7 +6621,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1.6"/>
@@ -6484,7 +6633,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-13.3"/>
@@ -6496,7 +6645,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-23.2"/>
@@ -6508,7 +6657,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-25.1"/>
@@ -6520,7 +6669,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-21.4"/>
@@ -6532,7 +6681,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -6544,7 +6693,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -6556,7 +6705,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -6568,7 +6717,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -6580,7 +6729,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -6592,7 +6741,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -6748,7 +6897,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>QXO(건자재 유통): TopBuild $170억 인수완료 30% 희석+주택착공허가 2.4% 감소로 신저가</t>
         </is>
@@ -6801,7 +6950,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>하니웰 에어로스페이스(항공우주 부품 분사): UBS 중립(목표 $231) 개시로 기대 미달, -4%대 급락</t>
         </is>
@@ -6852,7 +7001,7 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>워너브라더스 디스커버리(미디어·스트리밍): 파라마운트·스카이댄스 $1100억 딜 8/3까지 법원 중단명령</t>
         </is>
@@ -6905,7 +7054,7 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>링컨일렉트릭(산업용 용접장비): 수요 부진·고밸류 부담, 7/30 실적 앞 관망 신저가</t>
         </is>
@@ -6958,7 +7107,7 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>아스트라제네카(글로벌 제약): CARDIO-TTRansform 임상3상 1차 평가변수 실패 여파, 7/27 실적 앞 불안</t>
         </is>
@@ -7009,7 +7158,7 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -7062,7 +7211,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -7111,7 +7260,7 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -7164,7 +7313,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr"/>
+      <c r="M10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -7217,7 +7366,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr"/>
+      <c r="M11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -7268,7 +7417,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr"/>
+      <c r="M12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -7315,7 +7464,7 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>(전일) 2Q 실적 미스+호주 제련소 사고로 알루미나 가이던스 하향</t>
         </is>
@@ -7368,7 +7517,7 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="7" t="inlineStr"/>
+      <c r="M14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -7421,7 +7570,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>(전일) 개별 촉매 없이 바이오 섹터 매도세 속 52주 신저가</t>
         </is>
@@ -7476,7 +7625,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>(전일) HCA發 수술량 둔화 우려·목표가 인하($585→$520), 7/16 실적 앞 매도</t>
         </is>
@@ -7533,7 +7682,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>플레인스올아메리칸(원유·NGL 파이프라인 MLP): 바클레이즈 목표가 $21→$23 상향+트루이스트 매수 재확인</t>
         </is>
@@ -7586,7 +7735,7 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>AES(글로벌 발전·재생에너지 유틸리티): 7/15 분기배당 선언+재생에너지 확장, 7/30 실적 기대</t>
         </is>
@@ -7639,7 +7788,7 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>클린하버스(산업폐기물·환경서비스): 창업자 회장 퇴임 거버넌스 전환 속 신고가 지속</t>
         </is>
@@ -7696,7 +7845,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>브라이트스프링(재택·전문약국 헬스케어): S&amp;P400 편입(7/17)+증권사 목표가 상향, 신고가 후 소폭 조정</t>
         </is>
@@ -7749,7 +7898,7 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>리버티 포뮬러원(F1 미디어·중계권): 목표가 $100→$120 상향 불구 시장 전반 차익실현 매도</t>
         </is>
@@ -7802,7 +7951,7 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="7" t="inlineStr"/>
+      <c r="M22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -7851,7 +8000,7 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="7" t="inlineStr"/>
+      <c r="M23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -7904,7 +8053,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr"/>
+      <c r="M24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -7957,7 +8106,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr"/>
+      <c r="M25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -8010,7 +8159,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>(전일) 정유·에너지 섹터 강세 동반(개별 뉴스 미확인)</t>
         </is>
@@ -8067,7 +8216,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="M27" s="8" t="inlineStr">
         <is>
           <t>(전일) 정제마진 강세 지속, 애널리스트 목표가 상향 랠리</t>
         </is>
@@ -8118,7 +8267,7 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="7" t="inlineStr"/>
+      <c r="M28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -8171,7 +8320,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="M29" s="8" t="inlineStr">
         <is>
           <t>(전일) 정제 업황 호조, Raymond James TP $235 상향·정유 동반 강세</t>
         </is>
@@ -8228,7 +8377,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -8281,7 +8430,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr"/>
+      <c r="M31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -8332,7 +8481,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr"/>
+      <c r="M32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -8385,7 +8534,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr">
+      <c r="M33" s="8" t="inlineStr">
         <is>
           <t>(전일) 2Q EPS $10.04(예상 $5.34) 대폭 서프라이즈, 재해손실 감소 +8%</t>
         </is>
@@ -8442,7 +8591,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr"/>
+      <c r="M34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -8495,7 +8644,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr">
+      <c r="M35" s="8" t="inlineStr">
         <is>
           <t>(전일) General Mills·월마트 재생농업 제휴 발표+BMO 목표가 상향</t>
         </is>
@@ -8552,7 +8701,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr"/>
+      <c r="M36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -8605,7 +8754,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr"/>
+      <c r="M37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -8658,7 +8807,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr"/>
+      <c r="M38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -8711,7 +8860,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr"/>
+      <c r="M39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -8764,7 +8913,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr"/>
+      <c r="M40" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M40"/>
@@ -8914,7 +9063,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>손포홀딩스(손해보험 지주): 보험섹터 강세·690억엔 자사주매입 지속으로 수급 개선</t>
         </is>
@@ -8967,7 +9116,7 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>닛폰스틸(일본 최대 철강): US스틸 철강가 호조·FY27 이익 1000억엔 기여 기대로 자율반등</t>
         </is>
@@ -9018,7 +9167,7 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>다케다약품(일본 최대 제약): 7/2 인실리코 AI 신약발굴 딜(~$600M)+7/30 결산 앞둔 매수</t>
         </is>
@@ -9071,7 +9220,7 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>캐논(카메라·사무기기·반도체 노광): 광범위 자율반등+7/27 결산 앞둔 매수</t>
         </is>
@@ -9124,7 +9273,7 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>다이이치산쿄(제약, ADC 항암 강자): 6/29 EU 다토포타마브 승인권고+I-DXd FDA 우선심사 모멘텀</t>
         </is>
@@ -9177,7 +9326,7 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -9230,7 +9379,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -9283,7 +9432,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -9332,7 +9481,7 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>(전일) 디펜시브 소비재로 급락장서 상대적 견조, 60일 신고가</t>
         </is>
@@ -9389,7 +9538,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="M11" s="8" t="inlineStr">
         <is>
           <t>(전일) 기계·비철 급락장서 고배당 디펜시브로 상대 자금 유입</t>
         </is>
@@ -9539,7 +9688,7 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>(전일) 탄산리튬 가격 3월래 최저(칠레 수출증가·CATL 광산 재가동 공급과잉 우려)</t>
         </is>
@@ -9596,7 +9745,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>(전일) 골드만 하반기 리튬 20%+ 공급과잉 전망 등 공급증가 우려</t>
         </is>
@@ -9649,7 +9798,7 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>(전일) 노무라 경쟁심화 경고·광섬유 가격 둔화 우려, 고점 차익실현</t>
         </is>
@@ -9704,7 +9853,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>(전일) PCB·전자부품 섹터 급락(A주 동종 다수 하한가) 동반 하락</t>
         </is>
@@ -9757,7 +9906,7 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>SITC(아시아 역내 컨테이너 해운): 컨테이너 운임 4년래 고점·중동 리스크로 역내 운임 반등 수혜</t>
         </is>
@@ -9814,7 +9963,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>메이디그룹(종합가전 세계 1위): 유럽 폭염 에어컨 수출 급증(서유럽 +70%)·자사주 매입 지지</t>
         </is>
@@ -9962,7 +10111,7 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>더밍리(메모리 저장모듈): 2분기 순이익 전분기比 감소(-6~30%)+美 메모리주 급락 연동, 신저가 후 반등</t>
         </is>
@@ -10015,7 +10164,7 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>톈치리튬(리튬 채굴·가공): 리튬가격 지속 하락·기관 확정매도로 신저가 후 반등</t>
         </is>
@@ -10068,7 +10217,7 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>ZTE 중싱통신(통신장비): 1분기 순이익 -47% YoY·5G사이클 조정으로 신저가 후 반등</t>
         </is>
@@ -10121,7 +10270,7 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>셰촹데이터(데이터 저장장치·IDC장비): 6월 80억위안 유상증자 계획 희석우려로 신저가 후 반등</t>
         </is>
@@ -10174,7 +10323,7 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>중톈테크(광통신 케이블): 상반기 순이익 +50~60% 예증·7/17 자사주매입으로 하한가 후 낙폭회복</t>
         </is>
@@ -10227,7 +10376,7 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -10276,7 +10425,7 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="7" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -10323,7 +10472,7 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -10372,7 +10521,7 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="7" t="inlineStr"/>
+      <c r="M10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -10421,7 +10570,7 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="7" t="inlineStr"/>
+      <c r="M11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -10470,7 +10619,7 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="7" t="inlineStr"/>
+      <c r="M12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -10519,7 +10668,7 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr"/>
+      <c r="M13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -10568,7 +10717,7 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="7" t="inlineStr"/>
+      <c r="M14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -10617,7 +10766,7 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="7" t="inlineStr"/>
+      <c r="M15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -10666,7 +10815,7 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="7" t="inlineStr"/>
+      <c r="M16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -10715,7 +10864,7 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="7" t="inlineStr"/>
+      <c r="M17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -10764,7 +10913,7 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="7" t="inlineStr"/>
+      <c r="M18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -10815,7 +10964,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr"/>
+      <c r="M19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -10866,7 +11015,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>(전일) IPO 직후 급락 지속: 패널 업황·370억위안 부채·해금 부담(7/3~7 이상변동)</t>
         </is>
@@ -10919,7 +11068,7 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="7" t="inlineStr"/>
+      <c r="M21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -10968,7 +11117,7 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="7" t="inlineStr"/>
+      <c r="M22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -11017,7 +11166,7 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>(전일) 1Q 순손실 확대(-77% YoY), 상업우주 테마 고점 차익실현</t>
         </is>
@@ -11070,7 +11219,7 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="7" t="inlineStr">
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t>(전일) 1Q26 순이익 -62% 급감·주력자금 순유출, 고평가(PE 300배+) 부담 조정</t>
         </is>
@@ -11125,7 +11274,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>(전일) 7/13 급락(-13%) 후 차익실현·주력자금 순유출 지속</t>
         </is>
@@ -11178,7 +11327,7 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="7" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>(전일) 탄산리튬 가격 약세 지속·리튬 섹터 수급 부진</t>
         </is>
@@ -11231,7 +11380,7 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="M27" s="8" t="inlineStr">
         <is>
           <t>(전일) 1Q 순익 -30.7%·환차손 확대, 주력자금 순매도</t>
         </is>
@@ -11284,7 +11433,7 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="7" t="inlineStr"/>
+      <c r="M28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -11333,7 +11482,7 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="7" t="inlineStr"/>
+      <c r="M29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -11382,7 +11531,7 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="7" t="inlineStr">
+      <c r="M30" s="8" t="inlineStr">
         <is>
           <t>(전일) 반기 가이던스(+25~45%)가 기관 예상(68%) 하회, PE 106배 해소</t>
         </is>
@@ -11435,7 +11584,7 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="7" t="inlineStr">
+      <c r="M31" s="8" t="inlineStr">
         <is>
           <t>(전일) 반기 순익 +3200% 예고에도 대주주 감자 계획·고밸류 차익실현</t>
         </is>
@@ -11492,7 +11641,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr">
+      <c r="M32" s="8" t="inlineStr">
         <is>
           <t>쯔광구펀(H3C 서버·네트워크장비): AI연산 수요·H3C 매출급증+상반기 순이익 83~123% 증가 예고로 연속 상한가</t>
         </is>
@@ -11545,7 +11694,7 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="7" t="inlineStr">
+      <c r="M33" s="8" t="inlineStr">
         <is>
           <t>하이얼스마트홈(종합가전): 이구환신(가전 교체보조) 정책 수혜·글로벌 판매 견조로 신고가</t>
         </is>
@@ -11598,7 +11747,7 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="7" t="inlineStr">
+      <c r="M34" s="8" t="inlineStr">
         <is>
           <t>화능란창장수전(윈난 수력발전): 상반기 발전량 +4.14%·홍수기 호조로 신고가</t>
         </is>
@@ -11651,7 +11800,7 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="7" t="inlineStr">
+      <c r="M35" s="8" t="inlineStr">
         <is>
           <t>상하이항만그룹(상하이항 운영): 7/20 상반기 예증(컨테이너 물동량 +6.2% YoY) 반영 신고가</t>
         </is>
@@ -11704,7 +11853,7 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="7" t="inlineStr">
+      <c r="M36" s="8" t="inlineStr">
         <is>
           <t>그리전기(에어컨 대표주): 1분기 실적 안정·채널개혁 기대로 섹터 수급 신고가</t>
         </is>
@@ -11761,7 +11910,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr"/>
+      <c r="M37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -11814,7 +11963,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr"/>
+      <c r="M38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -11863,7 +12012,7 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="7" t="inlineStr"/>
+      <c r="M39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -11912,7 +12061,7 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="7" t="inlineStr"/>
+      <c r="M40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -11959,7 +12108,7 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="7" t="inlineStr"/>
+      <c r="M41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -12008,7 +12157,7 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="7" t="inlineStr">
+      <c r="M42" s="8" t="inlineStr">
         <is>
           <t>(전일) 야룽장 유역 강수 증가로 수력 발전량 상승 기대</t>
         </is>

--- a/신고신저가_20260721.xlsx
+++ b/신고신저가_20260721.xlsx
@@ -3477,72 +3477,72 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XLB US</t>
+          <t>XLK US</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>소재</t>
+          <t>테크</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>섹터 내 최약(-1.0%). 비에너지 광물·금속 신저 다발(순강도-2). 주간·1개월도 마이너스로 약세 지속.</t>
+          <t>보합(+0.1%). SW·IT서비스는 신고 우위(순강도+2), 반도체·전자하드웨어는 신저 다발(-2)로 내부 혼조. 주간 -3.1%.</t>
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>-1.1</v>
+        <v>-3.1</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>-3.5</v>
+        <v>-5.3</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>-3.2</v>
+        <v>14</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>11.2</v>
+        <v>22.3</v>
       </c>
       <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" s="7" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="7" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" s="7" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="L2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M2" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>11</v>
-      </c>
       <c r="O2" s="7" t="n">
-        <v>12.5</v>
+        <v>56</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>-12.3</v>
+        <v>-27.7</v>
       </c>
       <c r="R2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>27.4</v>
+        <v>34.7</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>20.5</v>
+        <v>43.6</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3629,72 +3629,72 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XLE US</t>
+          <t>XLF US</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>강세(+0.5%). 에너지광물 신고 4개(순강도+4), 원유 인프라 PAA(파이프라인) 신고가 — 시장 약세 속 상대 강세.</t>
+          <t>ETF는 소폭 하락(-0.4%)이나 은행·보험 신고가 6개로 시장 내 최다(순강도+6) — 개별 강세 지속, 방어 우위.</t>
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>6.7</v>
+        <v>4</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>31.4</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>7.9</v>
+        <v>14.9</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>5.6</v>
+        <v>30.6</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>-0.6</v>
+        <v>12</v>
       </c>
       <c r="P4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q4" s="7" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S4" s="7" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" s="7" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="V4" t="n">
         <v>9</v>
-      </c>
-      <c r="Q4" s="7" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="7" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" s="7" t="n">
-        <v>-32.7</v>
-      </c>
-      <c r="V4" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -3705,72 +3705,72 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XLK US</t>
+          <t>XLY US</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>테크</t>
+          <t>경기소비재</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>보합(+0.1%). SW·IT서비스는 신고 우위(순강도+2), 반도체·전자하드웨어는 신저 다발(-2)로 내부 혼조. 주간 -3.1%.</t>
+          <t>약세(-0.7%). 소비서비스·소매 신저(각 순강도-1), 내구재는 무신호. 경기민감 소비 상대 부진.</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-3.1</v>
+        <v>-1.2</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-5.3</v>
+        <v>-0.6</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>14</v>
+        <v>-4.6</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>22.3</v>
+        <v>-3.6</v>
       </c>
       <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>-36.3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>10</v>
+      </c>
+      <c r="S5" s="7" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" s="7" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="V5" t="n">
         <v>2</v>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="7" t="n">
-        <v>-27.7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>9</v>
-      </c>
-      <c r="S5" s="7" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" s="7" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3857,72 +3857,72 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XLRE US</t>
+          <t>XLI US</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>리츠</t>
+          <t>산업재</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>소폭 조정(-0.4%). 금리 민감 방어섹터, 개별 신고/신저 신호 미미 — 특별 촉매 없음.</t>
+          <t>약세(-0.7%). 자본재 신저, 링컨일렉트릭(용접) -2.9%·하니웰에어로 -4.3%. 운송·산업서비스는 신고로 혼재.</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1.2</v>
+        <v>-1.2</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3.8</v>
+        <v>-0.6</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>13.8</v>
+        <v>15.4</v>
       </c>
       <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L7" t="n">
-        <v>10</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>9</v>
-      </c>
-      <c r="O7" s="7" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="Q7" s="7" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" s="7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" s="7" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="V7" t="n">
         <v>6</v>
-      </c>
-      <c r="Q7" s="7" t="n">
-        <v>-26.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S7" s="7" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" s="7" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -4009,72 +4009,72 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XLF US</t>
+          <t>XLE US</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>에너지</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>ETF는 소폭 하락(-0.4%)이나 은행·보험 신고가 6개로 시장 내 최다(순강도+6) — 개별 강세 지속, 방어 우위.</t>
+          <t>강세(+0.5%). 에너지광물 신고 4개(순강도+4), 원유 인프라 PAA(파이프라인) 신고가 — 시장 약세 속 상대 강세.</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.1</v>
+        <v>2.1</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>4</v>
+        <v>6.7</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>3.2</v>
+        <v>31.4</v>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="K9" s="7" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="P9" t="n">
-        <v>7</v>
-      </c>
       <c r="Q9" s="7" t="n">
-        <v>-10.6</v>
+        <v>64.3</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>34.8</v>
+        <v>53.3</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>-1.7</v>
+        <v>-32.7</v>
       </c>
       <c r="V9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -4161,72 +4161,72 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XLI US</t>
+          <t>XLB US</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>산업재</t>
+          <t>소재</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>약세(-0.7%). 자본재 신저, 링컨일렉트릭(용접) -2.9%·하니웰에어로 -4.3%. 운송·산업서비스는 신고로 혼재.</t>
+          <t>섹터 내 최약(-1.0%). 비에너지 광물·금속 신저 다발(순강도-2). 주간·1개월도 마이너스로 약세 지속.</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.6</v>
+        <v>-3.5</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>2.9</v>
+        <v>-3.2</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>15.4</v>
+        <v>11.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>19.3</v>
+        <v>9.9</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>17.3</v>
+        <v>0.1</v>
       </c>
       <c r="N11" t="n">
+        <v>11</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" s="7" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="O11" s="7" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="U11" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="V11" t="n">
         <v>4</v>
-      </c>
-      <c r="Q11" s="7" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>5</v>
-      </c>
-      <c r="S11" s="7" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>8</v>
-      </c>
-      <c r="U11" s="7" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -4237,72 +4237,72 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XLY US</t>
+          <t>XLRE US</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>경기소비재</t>
+          <t>리츠</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>약세(-0.7%). 소비서비스·소매 신저(각 순강도-1), 내구재는 무신호. 경기민감 소비 상대 부진.</t>
+          <t>소폭 조정(-0.4%). 금리 민감 방어섹터, 개별 신고/신저 신호 미미 — 특별 촉매 없음.</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>-0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>-1.2</v>
+        <v>1.2</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>-0.6</v>
+        <v>3.8</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-4.6</v>
+        <v>2.6</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-3.6</v>
+        <v>13.8</v>
       </c>
       <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="K12" s="7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="M12" s="7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="M12" s="7" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3</v>
-      </c>
       <c r="O12" s="7" t="n">
-        <v>39.6</v>
+        <v>12.4</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>-36.3</v>
+        <v>-26.2</v>
       </c>
       <c r="R12" t="n">
+        <v>8</v>
+      </c>
+      <c r="S12" s="7" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" s="7" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="V12" t="n">
         <v>10</v>
-      </c>
-      <c r="S12" s="7" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" s="7" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -4313,68 +4313,68 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1624 JP</t>
+          <t>1617 JP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>기계</t>
+          <t>식품</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="7" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-1.5</v>
+        <v>1.1</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-5.2</v>
+        <v>4.1</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-3.9</v>
+        <v>6.7</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>19</v>
+        <v>16.6</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>31.1</v>
+        <v>11.8</v>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M13" s="7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N13" t="n">
+        <v>14</v>
+      </c>
+      <c r="O13" s="7" t="n">
         <v>22.3</v>
       </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" s="7" t="n">
-        <v>33.9</v>
-      </c>
       <c r="P13" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>-9.9</v>
+        <v>6.4</v>
       </c>
       <c r="R13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="T13" t="n">
+        <v>11</v>
+      </c>
+      <c r="U13" s="7" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="V13" t="n">
         <v>9</v>
-      </c>
-      <c r="U13" s="7" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="V13" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -4457,68 +4457,68 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1632 JP</t>
+          <t>1619 JP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>금융(은행외)</t>
+          <t>건설·자재</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
       <c r="E15" s="7" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>2.9</v>
+        <v>-2.2</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>6.3</v>
+        <v>-5.5</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>13.7</v>
+        <v>0.2</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>28.9</v>
+        <v>10.4</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>21.4</v>
+        <v>42</v>
       </c>
       <c r="L15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>49</v>
+        <v>21.6</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>27.2</v>
+        <v>32</v>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>13.7</v>
+        <v>-2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>22.6</v>
+        <v>12.6</v>
       </c>
       <c r="T15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-3.6</v>
+        <v>-6.1</v>
       </c>
       <c r="V15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -4529,68 +4529,68 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1627 JP</t>
+          <t>1620 JP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>전력·가스</t>
+          <t>소재·화학</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="7" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="G16" s="7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N16" t="n">
+        <v>16</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q16" s="7" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>14</v>
+      </c>
+      <c r="S16" s="7" t="n">
         <v>2.1</v>
       </c>
-      <c r="H16" s="7" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>15</v>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="N16" t="n">
-        <v>15</v>
-      </c>
-      <c r="O16" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q16" s="7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7</v>
-      </c>
-      <c r="S16" s="7" t="n">
-        <v>-8.300000000000001</v>
-      </c>
       <c r="T16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>-10.7</v>
+        <v>8.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -4601,68 +4601,68 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1631 JP</t>
+          <t>1621 JP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>의약품</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="7" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>-0.6</v>
+        <v>2.6</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>6.1</v>
+        <v>7.2</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>18.8</v>
+        <v>-6.1</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>44.1</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>44.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>50.4</v>
+        <v>10.8</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>33.2</v>
+        <v>0.5</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>38.3</v>
+        <v>16.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>26.7</v>
+        <v>-8.4</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-16.3</v>
+        <v>4.6</v>
       </c>
       <c r="V17" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -4673,68 +4673,68 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1623 JP</t>
+          <t>1622 JP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>철강·비철</t>
+          <t>자동차·운송기기</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="7" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>-3.7</v>
+        <v>4.2</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>-22.5</v>
+        <v>6.3</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-17.2</v>
+        <v>-4.2</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>35.9</v>
+        <v>-4.7</v>
       </c>
       <c r="J18" t="n">
+        <v>17</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>14</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>11</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="K18" s="7" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="7" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="Q18" s="7" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>16</v>
+      </c>
+      <c r="S18" s="7" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V18" t="n">
         <v>8</v>
-      </c>
-      <c r="O18" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="P18" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="7" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>5</v>
-      </c>
-      <c r="S18" s="7" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T18" t="n">
-        <v>7</v>
-      </c>
-      <c r="U18" s="7" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="V18" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -4745,68 +4745,68 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1629 JP</t>
+          <t>1623 JP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>상사·도매</t>
+          <t>철강·비철</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
       <c r="E19" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="K19" s="7" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8</v>
+      </c>
+      <c r="O19" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="G19" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>9</v>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="Q19" s="7" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="M19" s="7" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>9</v>
-      </c>
-      <c r="O19" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="7" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3</v>
-      </c>
       <c r="S19" s="7" t="n">
-        <v>29.2</v>
+        <v>20.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>1.9</v>
+        <v>-8.6</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -4817,68 +4817,68 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1625 JP</t>
+          <t>1624 JP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>전기·정밀</t>
+          <t>기계</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="7" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>-3.8</v>
+        <v>-1.5</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>-10.1</v>
+        <v>-5.2</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>12.5</v>
+        <v>-3.9</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>30.2</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" s="7" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="P20" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="7" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="R20" t="n">
+        <v>15</v>
+      </c>
+      <c r="S20" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" s="7" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="V20" t="n">
         <v>3</v>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>9</v>
-      </c>
-      <c r="M20" s="7" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="N20" t="n">
-        <v>10</v>
-      </c>
-      <c r="O20" s="7" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="P20" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q20" s="7" t="n">
-        <v>-23</v>
-      </c>
-      <c r="R20" t="n">
-        <v>17</v>
-      </c>
-      <c r="S20" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U20" s="7" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1633 JP</t>
+          <t>1625 JP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>부동산</t>
+          <t>전기·정밀</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
       <c r="E21" s="7" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>2.8</v>
+        <v>-3.8</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>6.2</v>
+        <v>-10.1</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.6</v>
+        <v>30.2</v>
       </c>
       <c r="J21" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>41.6</v>
+        <v>27.5</v>
       </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>13.9</v>
+        <v>17.9</v>
       </c>
       <c r="N21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>23.6</v>
+        <v>33.7</v>
       </c>
       <c r="P21" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>4.4</v>
+        <v>-23</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="T21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>-13.3</v>
+        <v>26.2</v>
       </c>
       <c r="V21" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -4961,68 +4961,68 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1622 JP</t>
+          <t>1626 JP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>자동차·운송기기</t>
+          <t>정보통신·서비스</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
       <c r="E22" s="7" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>4.2</v>
+        <v>-0.8</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>-4.2</v>
+        <v>10.8</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-4.7</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="L22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>16.4</v>
+        <v>21</v>
       </c>
       <c r="N22" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>40.5</v>
+        <v>17.9</v>
       </c>
       <c r="P22" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q22" s="7" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>13</v>
+      </c>
+      <c r="S22" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>13</v>
+      </c>
+      <c r="U22" s="7" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="V22" t="n">
         <v>2</v>
-      </c>
-      <c r="Q22" s="7" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="R22" t="n">
-        <v>16</v>
-      </c>
-      <c r="S22" s="7" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="V22" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -5033,68 +5033,68 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1626 JP</t>
+          <t>1627 JP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>정보통신·서비스</t>
+          <t>전력·가스</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="7" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>-0.8</v>
+        <v>3.3</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>10.8</v>
+        <v>-8.9</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>13.9</v>
+        <v>37.4</v>
       </c>
       <c r="L23" t="n">
+        <v>7</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>15</v>
+      </c>
+      <c r="O23" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="7" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" s="7" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="T23" t="n">
+        <v>16</v>
+      </c>
+      <c r="U23" s="7" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="V23" t="n">
         <v>13</v>
-      </c>
-      <c r="M23" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="N23" t="n">
-        <v>7</v>
-      </c>
-      <c r="O23" s="7" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="P23" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q23" s="7" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>13</v>
-      </c>
-      <c r="S23" s="7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T23" t="n">
-        <v>13</v>
-      </c>
-      <c r="U23" s="7" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="V23" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -5105,68 +5105,68 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1619 JP</t>
+          <t>1628 JP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>건설·자재</t>
+          <t>운수·물류</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>-2.2</v>
+        <v>3.2</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>-5.5</v>
+        <v>8.5</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>10.4</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>42</v>
+        <v>19.9</v>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>21.6</v>
+        <v>-0</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="P24" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>-2.4</v>
+        <v>13.1</v>
       </c>
       <c r="R24" t="n">
+        <v>8</v>
+      </c>
+      <c r="S24" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="S24" s="7" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="T24" t="n">
-        <v>8</v>
-      </c>
       <c r="U24" s="7" t="n">
-        <v>-6.1</v>
+        <v>-17.1</v>
       </c>
       <c r="V24" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -5177,68 +5177,68 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1621 JP</t>
+          <t>1629 JP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>의약품</t>
+          <t>상사·도매</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="7" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-6.1</v>
+        <v>-7.7</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>2.9</v>
+        <v>13.1</v>
       </c>
       <c r="J25" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>41.5</v>
       </c>
       <c r="L25" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>10.8</v>
+        <v>20.1</v>
       </c>
       <c r="N25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>0.5</v>
+        <v>42</v>
       </c>
       <c r="P25" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>16.4</v>
+        <v>21.3</v>
       </c>
       <c r="R25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>-8.4</v>
+        <v>29.2</v>
       </c>
       <c r="T25" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -5249,68 +5249,68 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1628 JP</t>
+          <t>1630 JP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>운수·물류</t>
+          <t>소매</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="7" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>8.5</v>
+        <v>4.7</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="J26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>19.9</v>
+        <v>16.8</v>
       </c>
       <c r="L26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>-0</v>
+        <v>23.4</v>
       </c>
       <c r="N26" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>19</v>
+        <v>16.4</v>
       </c>
       <c r="P26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>13.1</v>
+        <v>10.2</v>
       </c>
       <c r="R26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>4.7</v>
+        <v>-4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U26" s="7" t="n">
-        <v>-17.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -5321,68 +5321,68 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1617 JP</t>
+          <t>1631 JP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>식품</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="7" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>1.1</v>
+        <v>-0.6</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>6.7</v>
+        <v>18.8</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>16.6</v>
+        <v>44.1</v>
       </c>
       <c r="J27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>11.8</v>
+        <v>44.8</v>
       </c>
       <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="7" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="P27" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" s="7" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" s="7" t="n">
+        <v>-16.3</v>
+      </c>
+      <c r="V27" t="n">
         <v>15</v>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="N27" t="n">
-        <v>14</v>
-      </c>
-      <c r="O27" s="7" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="P27" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q27" s="7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R27" t="n">
-        <v>10</v>
-      </c>
-      <c r="S27" s="7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="T27" t="n">
-        <v>11</v>
-      </c>
-      <c r="U27" s="7" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="V27" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -5393,68 +5393,68 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1620 JP</t>
+          <t>1632 JP</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>소재·화학</t>
+          <t>금융(은행외)</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="7" t="n">
-        <v>0.3</v>
+        <v>3.9</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>-0.5</v>
+        <v>6.3</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>6.6</v>
+        <v>13.7</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>24.2</v>
+        <v>28.9</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>8.6</v>
+        <v>21.4</v>
       </c>
       <c r="L28" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>3.9</v>
+        <v>49</v>
       </c>
       <c r="N28" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>23.1</v>
+        <v>27.2</v>
       </c>
       <c r="P28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>-9.4</v>
+        <v>13.7</v>
       </c>
       <c r="R28" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>2.1</v>
+        <v>22.6</v>
       </c>
       <c r="T28" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>8.6</v>
+        <v>-3.6</v>
       </c>
       <c r="V28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -5465,68 +5465,68 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1630 JP</t>
+          <t>1633 JP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>소매</t>
+          <t>부동산</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="7" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>1.9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="I29" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>16</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="N29" t="n">
+        <v>12</v>
+      </c>
+      <c r="O29" s="7" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="P29" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q29" s="7" t="n">
         <v>4.4</v>
       </c>
-      <c r="J29" t="n">
-        <v>12</v>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="L29" t="n">
-        <v>12</v>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="N29" t="n">
-        <v>4</v>
-      </c>
-      <c r="O29" s="7" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="P29" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q29" s="7" t="n">
-        <v>10.2</v>
-      </c>
       <c r="R29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>-4.4</v>
+        <v>6.8</v>
       </c>
       <c r="T29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>8.699999999999999</v>
+        <v>-13.3</v>
       </c>
       <c r="V29" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -5537,65 +5537,69 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3033 HK</t>
+          <t>2800 HK</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>항셍테크</t>
+          <t>항셍지수</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="n">
-        <v>1.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>-4.7</v>
+        <v>-2.6</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>-12.7</v>
+        <v>-0.3</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>22.7</v>
+        <v>32.8</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>18.9</v>
+        <v>24.8</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>-9.300000000000001</v>
+        <v>-11.9</v>
       </c>
       <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" s="7" t="n">
-        <v>-27.4</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3</v>
-      </c>
       <c r="S30" s="7" t="n">
-        <v>-32.9</v>
+        <v>-13.5</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
-      </c>
-      <c r="U30" s="7" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="U30" s="7" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5605,68 +5609,68 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2800 HK</t>
+          <t>2828 HK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>항셍지수</t>
+          <t>H주(중국기업)</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="7" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>2.9</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-2.6</v>
+        <v>-4.4</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>-0.3</v>
+        <v>-5.2</v>
       </c>
       <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" s="7" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" s="7" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="O31" s="7" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="O31" s="7" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="S31" s="7" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="Q31" s="7" t="n">
-        <v>-14.4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" s="7" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
       <c r="U31" s="7" t="n">
-        <v>-1.2</v>
+        <v>-2</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -5677,69 +5681,65 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2828 HK</t>
+          <t>3033 HK</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>H주(중국기업)</t>
+          <t>항셍테크</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="7" t="n">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>-4.4</v>
+        <v>-4.7</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>-5.2</v>
+        <v>-12.7</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>26.2</v>
+        <v>22.7</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>32.1</v>
+        <v>18.9</v>
       </c>
       <c r="N32" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="O32" s="7" t="n">
-        <v>-12.8</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="Q32" s="7" t="n">
+        <v>-27.4</v>
+      </c>
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" s="7" t="n">
-        <v>-17.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2</v>
-      </c>
       <c r="S32" s="7" t="n">
-        <v>-23.6</v>
+        <v>-32.9</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="V32" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="U32" s="7" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6616,7 +6616,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>※ 미국=SPDR 섹터 ETF, 일본=TOPIX-17 섹터 ETF(1617~1633), 중국A=주요 섹터 ETF(상해·심천) · 홍콩은 섹터 ETF가 얇아 시장·테크 대표만 · 수익률은 배당 포함 총수익 기준(미국=야후 수정주가, 중·홍=eastmoney 전복권) — 블룸버그 가격수익률과 고배당 섹터에서 연 1~2%p 차이 가능 · 시장별 1D 변동 1%↑는 위(상승→하락순)·1% 미만 보합은 아래로</t>
+          <t>※ 미국=SPDR 섹터 ETF, 일본=TOPIX-17 섹터 ETF(1617~1633), 중국A=주요 섹터 ETF(상해·심천) · 홍콩은 섹터 ETF가 얇아 시장·테크 대표만 · 수익률은 배당 포함 총수익 기준(미국=야후 수정주가, 중·홍=eastmoney 전복권) — 블룸버그 가격수익률과 고배당 섹터에서 연 1~2%p 차이 가능 · 정렬=시장·섹터 고정순(대시보드는 1D 등락순으로 표시)</t>
         </is>
       </c>
     </row>
